--- a/PCM_OS_Intranet.xlsx
+++ b/PCM_OS_Intranet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jasmine\Desktop\PCM-Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97D7EBCD-0720-419A-A65B-41D365B1AEE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84B8F9E2-D475-4A3F-80AC-18E72E1A022B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4503" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4501" uniqueCount="44">
   <si>
     <t>EXPORTAÇÃO DO INTRANET — COLE OS DADOS AQUI (não altere os cabeçalhos)</t>
   </si>
@@ -540,6 +540,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:K1004"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -609,7 +610,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>9576</v>
       </c>
@@ -644,7 +645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>9571</v>
       </c>
@@ -679,7 +680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>9571</v>
       </c>
@@ -714,7 +715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>9598</v>
       </c>
@@ -749,7 +750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>9713</v>
       </c>
@@ -784,7 +785,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>9722</v>
       </c>
@@ -819,7 +820,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>9418</v>
       </c>
@@ -854,7 +855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>10306</v>
       </c>
@@ -889,7 +890,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>10470</v>
       </c>
@@ -924,7 +925,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>10588</v>
       </c>
@@ -959,7 +960,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>10650</v>
       </c>
@@ -994,7 +995,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>9547</v>
       </c>
@@ -1029,7 +1030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>9667</v>
       </c>
@@ -1064,7 +1065,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>9750</v>
       </c>
@@ -1099,7 +1100,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>9995</v>
       </c>
@@ -1134,7 +1135,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>9486</v>
       </c>
@@ -1169,7 +1170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>9540</v>
       </c>
@@ -1204,7 +1205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>10220</v>
       </c>
@@ -1239,7 +1240,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>10344</v>
       </c>
@@ -1274,7 +1275,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>10459</v>
       </c>
@@ -1309,7 +1310,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>9595</v>
       </c>
@@ -1344,7 +1345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>9597</v>
       </c>
@@ -1379,7 +1380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>9623</v>
       </c>
@@ -1414,7 +1415,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>10306</v>
       </c>
@@ -1449,7 +1450,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>10507</v>
       </c>
@@ -1484,7 +1485,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>10582</v>
       </c>
@@ -1519,7 +1520,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>10657</v>
       </c>
@@ -1554,7 +1555,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>10728</v>
       </c>
@@ -1589,7 +1590,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>10824</v>
       </c>
@@ -1624,7 +1625,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>10909</v>
       </c>
@@ -1659,7 +1660,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>11079</v>
       </c>
@@ -1694,7 +1695,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>9463</v>
       </c>
@@ -1729,7 +1730,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>9488</v>
       </c>
@@ -1764,7 +1765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>9485</v>
       </c>
@@ -1799,7 +1800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>9481</v>
       </c>
@@ -1834,7 +1835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>9491</v>
       </c>
@@ -1869,7 +1870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>9519</v>
       </c>
@@ -1904,7 +1905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>9531</v>
       </c>
@@ -1939,7 +1940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <v>9541</v>
       </c>
@@ -1974,7 +1975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>9570</v>
       </c>
@@ -2009,7 +2010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <v>9569</v>
       </c>
@@ -2044,7 +2045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <v>9562</v>
       </c>
@@ -2079,7 +2080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
         <v>9561</v>
       </c>
@@ -2114,7 +2115,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <v>9560</v>
       </c>
@@ -2149,7 +2150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <v>9587</v>
       </c>
@@ -2184,7 +2185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <v>9600</v>
       </c>
@@ -2219,7 +2220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
         <v>9599</v>
       </c>
@@ -2254,7 +2255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <v>9605</v>
       </c>
@@ -2289,7 +2290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
         <v>9616</v>
       </c>
@@ -2324,7 +2325,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
         <v>9618</v>
       </c>
@@ -2359,7 +2360,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
         <v>9625</v>
       </c>
@@ -2394,7 +2395,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
         <v>9629</v>
       </c>
@@ -2429,7 +2430,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
         <v>9631</v>
       </c>
@@ -2464,7 +2465,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
         <v>9632</v>
       </c>
@@ -2499,7 +2500,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
         <v>9633</v>
       </c>
@@ -2534,7 +2535,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
         <v>9636</v>
       </c>
@@ -2569,7 +2570,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
         <v>9637</v>
       </c>
@@ -2604,7 +2605,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
         <v>9640</v>
       </c>
@@ -2639,7 +2640,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
         <v>9652</v>
       </c>
@@ -2674,7 +2675,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
         <v>9662</v>
       </c>
@@ -2709,7 +2710,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
         <v>9666</v>
       </c>
@@ -2744,7 +2745,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
         <v>9670</v>
       </c>
@@ -2779,7 +2780,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
         <v>9676</v>
       </c>
@@ -2814,7 +2815,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
         <v>9678</v>
       </c>
@@ -2849,7 +2850,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
         <v>9681</v>
       </c>
@@ -2884,7 +2885,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
         <v>9682</v>
       </c>
@@ -2919,7 +2920,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="3">
         <v>9686</v>
       </c>
@@ -2954,7 +2955,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
         <v>9689</v>
       </c>
@@ -2989,7 +2990,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="3">
         <v>9692</v>
       </c>
@@ -3024,7 +3025,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
         <v>9693</v>
       </c>
@@ -3059,7 +3060,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
         <v>9698</v>
       </c>
@@ -3094,7 +3095,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3">
         <v>9709</v>
       </c>
@@ -3129,7 +3130,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="3">
         <v>9710</v>
       </c>
@@ -3164,7 +3165,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="3">
         <v>9711</v>
       </c>
@@ -3199,7 +3200,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
         <v>9723</v>
       </c>
@@ -3234,7 +3235,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
         <v>9744</v>
       </c>
@@ -3269,7 +3270,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
         <v>9790</v>
       </c>
@@ -3304,7 +3305,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
         <v>9922</v>
       </c>
@@ -3339,7 +3340,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="3">
         <v>9981</v>
       </c>
@@ -3374,7 +3375,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
         <v>9986</v>
       </c>
@@ -3409,7 +3410,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
         <v>10011</v>
       </c>
@@ -3444,7 +3445,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3">
         <v>10163</v>
       </c>
@@ -3479,7 +3480,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="3">
         <v>10242</v>
       </c>
@@ -3514,7 +3515,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
         <v>10334</v>
       </c>
@@ -3549,7 +3550,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="3">
         <v>10357</v>
       </c>
@@ -3584,7 +3585,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
         <v>10357</v>
       </c>
@@ -3619,7 +3620,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="3">
         <v>10368</v>
       </c>
@@ -3654,7 +3655,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
         <v>10611</v>
       </c>
@@ -3689,7 +3690,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="3">
         <v>10699</v>
       </c>
@@ -3724,7 +3725,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="3">
         <v>10679</v>
       </c>
@@ -3759,7 +3760,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="3">
         <v>10703</v>
       </c>
@@ -3794,7 +3795,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="3">
         <v>10713</v>
       </c>
@@ -3829,7 +3830,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="3">
         <v>9390</v>
       </c>
@@ -3864,7 +3865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="3">
         <v>9389</v>
       </c>
@@ -3899,7 +3900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="3">
         <v>9388</v>
       </c>
@@ -3934,7 +3935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="3">
         <v>9406</v>
       </c>
@@ -3969,7 +3970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="3">
         <v>9405</v>
       </c>
@@ -4004,7 +4005,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="3">
         <v>9404</v>
       </c>
@@ -4039,7 +4040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="3">
         <v>9401</v>
       </c>
@@ -4074,7 +4075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="3">
         <v>9400</v>
       </c>
@@ -4109,7 +4110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="3">
         <v>9398</v>
       </c>
@@ -4144,7 +4145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="3">
         <v>9397</v>
       </c>
@@ -4179,7 +4180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="3">
         <v>9396</v>
       </c>
@@ -4214,7 +4215,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="3">
         <v>9416</v>
       </c>
@@ -4249,7 +4250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="3">
         <v>9414</v>
       </c>
@@ -4284,7 +4285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="3">
         <v>9417</v>
       </c>
@@ -4319,7 +4320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="3">
         <v>9437</v>
       </c>
@@ -4354,7 +4355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="3">
         <v>9436</v>
       </c>
@@ -4389,7 +4390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="3">
         <v>9435</v>
       </c>
@@ -4424,7 +4425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="3">
         <v>9440</v>
       </c>
@@ -4459,7 +4460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="3">
         <v>9447</v>
       </c>
@@ -4494,7 +4495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="3">
         <v>9460</v>
       </c>
@@ -4529,7 +4530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="3">
         <v>9459</v>
       </c>
@@ -4564,7 +4565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="3">
         <v>9451</v>
       </c>
@@ -4599,7 +4600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="3">
         <v>9465</v>
       </c>
@@ -4634,7 +4635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="3">
         <v>9464</v>
       </c>
@@ -4669,7 +4670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="3">
         <v>9462</v>
       </c>
@@ -4704,7 +4705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="3">
         <v>9487</v>
       </c>
@@ -4739,7 +4740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="3">
         <v>9484</v>
       </c>
@@ -4774,7 +4775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="3">
         <v>9482</v>
       </c>
@@ -4809,7 +4810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="3">
         <v>9480</v>
       </c>
@@ -4844,7 +4845,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="3">
         <v>9490</v>
       </c>
@@ -4879,7 +4880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="3">
         <v>9501</v>
       </c>
@@ -4914,7 +4915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="3">
         <v>9502</v>
       </c>
@@ -4949,7 +4950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="3">
         <v>9520</v>
       </c>
@@ -4984,7 +4985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="3">
         <v>9516</v>
       </c>
@@ -5019,7 +5020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="3">
         <v>9515</v>
       </c>
@@ -5054,7 +5055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="3">
         <v>9514</v>
       </c>
@@ -5089,7 +5090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="3">
         <v>9513</v>
       </c>
@@ -5124,7 +5125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="3">
         <v>9512</v>
       </c>
@@ -5159,7 +5160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="3">
         <v>9510</v>
       </c>
@@ -5194,7 +5195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="3">
         <v>9524</v>
       </c>
@@ -5229,7 +5230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="3">
         <v>9523</v>
       </c>
@@ -5264,7 +5265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="3">
         <v>9539</v>
       </c>
@@ -5299,7 +5300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="3">
         <v>9538</v>
       </c>
@@ -5334,7 +5335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="3">
         <v>9549</v>
       </c>
@@ -5369,7 +5370,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="3">
         <v>9553</v>
       </c>
@@ -5404,7 +5405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="3">
         <v>9551</v>
       </c>
@@ -5439,7 +5440,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="3">
         <v>9554</v>
       </c>
@@ -5474,7 +5475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="3">
         <v>9575</v>
       </c>
@@ -5509,7 +5510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="3">
         <v>9574</v>
       </c>
@@ -5544,7 +5545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="3">
         <v>9568</v>
       </c>
@@ -5579,7 +5580,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="3">
         <v>9588</v>
       </c>
@@ -5614,7 +5615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="3">
         <v>9586</v>
       </c>
@@ -5649,7 +5650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="3">
         <v>9585</v>
       </c>
@@ -5684,7 +5685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="3">
         <v>9584</v>
       </c>
@@ -5719,7 +5720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="3">
         <v>9582</v>
       </c>
@@ -5754,7 +5755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="3">
         <v>9580</v>
       </c>
@@ -5789,7 +5790,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="3">
         <v>9579</v>
       </c>
@@ -5824,7 +5825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="3">
         <v>9578</v>
       </c>
@@ -5859,7 +5860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="3">
         <v>9596</v>
       </c>
@@ -5894,7 +5895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="3">
         <v>9606</v>
       </c>
@@ -5929,7 +5930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="3">
         <v>9614</v>
       </c>
@@ -5964,7 +5965,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="3">
         <v>9619</v>
       </c>
@@ -5999,7 +6000,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="3">
         <v>9620</v>
       </c>
@@ -6034,7 +6035,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="3">
         <v>9622</v>
       </c>
@@ -6069,7 +6070,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="3">
         <v>9639</v>
       </c>
@@ -6104,7 +6105,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="3">
         <v>9641</v>
       </c>
@@ -6139,7 +6140,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" s="3">
         <v>9642</v>
       </c>
@@ -6174,7 +6175,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" s="3">
         <v>9648</v>
       </c>
@@ -6209,7 +6210,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="3">
         <v>9654</v>
       </c>
@@ -6244,7 +6245,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" s="3">
         <v>9663</v>
       </c>
@@ -6279,7 +6280,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="3">
         <v>9669</v>
       </c>
@@ -6314,7 +6315,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="3">
         <v>9672</v>
       </c>
@@ -6349,7 +6350,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="3">
         <v>9677</v>
       </c>
@@ -6384,7 +6385,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="3">
         <v>9679</v>
       </c>
@@ -6419,7 +6420,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="3">
         <v>9680</v>
       </c>
@@ -6454,7 +6455,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="3">
         <v>9684</v>
       </c>
@@ -6489,7 +6490,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="3">
         <v>9688</v>
       </c>
@@ -6524,7 +6525,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="3">
         <v>9690</v>
       </c>
@@ -6559,7 +6560,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="3">
         <v>9691</v>
       </c>
@@ -6594,7 +6595,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="3">
         <v>9701</v>
       </c>
@@ -6629,7 +6630,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="3">
         <v>9702</v>
       </c>
@@ -6664,7 +6665,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="3">
         <v>9703</v>
       </c>
@@ -6699,7 +6700,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="3">
         <v>9704</v>
       </c>
@@ -6734,7 +6735,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="3">
         <v>9705</v>
       </c>
@@ -6769,7 +6770,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="3">
         <v>9706</v>
       </c>
@@ -6804,7 +6805,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="3">
         <v>9715</v>
       </c>
@@ -6839,7 +6840,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="3">
         <v>9716</v>
       </c>
@@ -6874,7 +6875,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="3">
         <v>9719</v>
       </c>
@@ -6909,7 +6910,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="3">
         <v>9721</v>
       </c>
@@ -6944,7 +6945,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="3">
         <v>9726</v>
       </c>
@@ -6979,7 +6980,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" s="3">
         <v>9729</v>
       </c>
@@ -7014,7 +7015,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" s="3">
         <v>9732</v>
       </c>
@@ -7049,7 +7050,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" s="3">
         <v>9733</v>
       </c>
@@ -7084,7 +7085,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="3">
         <v>9734</v>
       </c>
@@ -7119,7 +7120,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="3">
         <v>9735</v>
       </c>
@@ -7154,7 +7155,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" s="3">
         <v>9738</v>
       </c>
@@ -7189,7 +7190,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" s="3">
         <v>9739</v>
       </c>
@@ -7224,7 +7225,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" s="3">
         <v>9741</v>
       </c>
@@ -7259,7 +7260,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" s="3">
         <v>9742</v>
       </c>
@@ -7294,7 +7295,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" s="3">
         <v>9745</v>
       </c>
@@ -7329,7 +7330,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" s="3">
         <v>9749</v>
       </c>
@@ -7364,7 +7365,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" s="3">
         <v>9751</v>
       </c>
@@ -7399,7 +7400,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" s="3">
         <v>9754</v>
       </c>
@@ -7434,7 +7435,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" s="3">
         <v>9755</v>
       </c>
@@ -7469,7 +7470,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" s="3">
         <v>9756</v>
       </c>
@@ -7504,7 +7505,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" s="3">
         <v>9757</v>
       </c>
@@ -7539,7 +7540,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="3">
         <v>9758</v>
       </c>
@@ -7574,7 +7575,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" s="3">
         <v>9759</v>
       </c>
@@ -7609,7 +7610,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" s="3">
         <v>9810</v>
       </c>
@@ -7644,7 +7645,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" s="3">
         <v>9816</v>
       </c>
@@ -7679,7 +7680,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" s="3">
         <v>9818</v>
       </c>
@@ -7714,7 +7715,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" s="3">
         <v>9828</v>
       </c>
@@ -7749,7 +7750,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" s="3">
         <v>9829</v>
       </c>
@@ -7784,7 +7785,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" s="3">
         <v>9876</v>
       </c>
@@ -7819,7 +7820,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" s="3">
         <v>9875</v>
       </c>
@@ -7854,7 +7855,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" s="3">
         <v>9874</v>
       </c>
@@ -7889,7 +7890,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" s="3">
         <v>9873</v>
       </c>
@@ -7924,7 +7925,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" s="3">
         <v>9857</v>
       </c>
@@ -7959,7 +7960,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" s="3">
         <v>9856</v>
       </c>
@@ -7994,7 +7995,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" s="3">
         <v>9854</v>
       </c>
@@ -8029,7 +8030,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" s="3">
         <v>9850</v>
       </c>
@@ -8064,7 +8065,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" s="3">
         <v>9843</v>
       </c>
@@ -8099,7 +8100,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" s="3">
         <v>9842</v>
       </c>
@@ -8134,7 +8135,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" s="3">
         <v>9841</v>
       </c>
@@ -8169,7 +8170,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" s="3">
         <v>9840</v>
       </c>
@@ -8204,7 +8205,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" s="3">
         <v>9887</v>
       </c>
@@ -8239,7 +8240,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" s="3">
         <v>9883</v>
       </c>
@@ -8274,7 +8275,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" s="3">
         <v>9879</v>
       </c>
@@ -8309,7 +8310,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" s="3">
         <v>9911</v>
       </c>
@@ -8344,7 +8345,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" s="3">
         <v>9909</v>
       </c>
@@ -8379,7 +8380,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" s="3">
         <v>9907</v>
       </c>
@@ -8414,7 +8415,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" s="3">
         <v>9968</v>
       </c>
@@ -8449,7 +8450,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" s="3">
         <v>9988</v>
       </c>
@@ -8484,7 +8485,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" s="3">
         <v>9987</v>
       </c>
@@ -8519,7 +8520,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" s="3">
         <v>9985</v>
       </c>
@@ -8554,7 +8555,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" s="3">
         <v>10000</v>
       </c>
@@ -8589,7 +8590,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" s="3">
         <v>9999</v>
       </c>
@@ -8624,7 +8625,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" s="3">
         <v>9998</v>
       </c>
@@ -8659,7 +8660,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" s="3">
         <v>10004</v>
       </c>
@@ -8694,7 +8695,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" s="3">
         <v>10003</v>
       </c>
@@ -8729,7 +8730,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" s="3">
         <v>10018</v>
       </c>
@@ -8764,7 +8765,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" s="3">
         <v>10017</v>
       </c>
@@ -8799,7 +8800,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" s="3">
         <v>10013</v>
       </c>
@@ -8834,7 +8835,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" s="3">
         <v>10012</v>
       </c>
@@ -8869,7 +8870,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" s="3">
         <v>10033</v>
       </c>
@@ -8904,7 +8905,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" s="3">
         <v>10032</v>
       </c>
@@ -8939,7 +8940,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" s="3">
         <v>10031</v>
       </c>
@@ -8974,7 +8975,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" s="3">
         <v>10030</v>
       </c>
@@ -9009,7 +9010,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" s="3">
         <v>10049</v>
       </c>
@@ -9044,7 +9045,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" s="3">
         <v>10048</v>
       </c>
@@ -9079,7 +9080,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" s="3">
         <v>10158</v>
       </c>
@@ -9114,7 +9115,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" s="3">
         <v>10156</v>
       </c>
@@ -9149,7 +9150,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" s="3">
         <v>10164</v>
       </c>
@@ -9184,7 +9185,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" s="3">
         <v>10176</v>
       </c>
@@ -9219,7 +9220,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" s="3">
         <v>10174</v>
       </c>
@@ -9254,7 +9255,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" s="3">
         <v>10172</v>
       </c>
@@ -9289,7 +9290,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" s="3">
         <v>10200</v>
       </c>
@@ -9324,7 +9325,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" s="3">
         <v>10201</v>
       </c>
@@ -9359,7 +9360,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" s="3">
         <v>10231</v>
       </c>
@@ -9394,7 +9395,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="255" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" s="3">
         <v>10232</v>
       </c>
@@ -9429,7 +9430,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" s="3">
         <v>10233</v>
       </c>
@@ -9464,7 +9465,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="257" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" s="3">
         <v>10240</v>
       </c>
@@ -9499,7 +9500,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="258" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" s="3">
         <v>10243</v>
       </c>
@@ -9534,7 +9535,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="259" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" s="3">
         <v>10245</v>
       </c>
@@ -9569,7 +9570,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="260" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" s="3">
         <v>10254</v>
       </c>
@@ -9604,7 +9605,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="261" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" s="3">
         <v>10255</v>
       </c>
@@ -9639,7 +9640,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="262" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" s="3">
         <v>10268</v>
       </c>
@@ -9674,7 +9675,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="263" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" s="3">
         <v>10269</v>
       </c>
@@ -9709,7 +9710,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="264" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" s="3">
         <v>10271</v>
       </c>
@@ -9744,7 +9745,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="265" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" s="3">
         <v>10272</v>
       </c>
@@ -9779,7 +9780,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="266" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" s="3">
         <v>10273</v>
       </c>
@@ -9814,7 +9815,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="267" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" s="3">
         <v>10275</v>
       </c>
@@ -9849,7 +9850,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="268" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" s="3">
         <v>10276</v>
       </c>
@@ -9884,7 +9885,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="269" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" s="3">
         <v>10287</v>
       </c>
@@ -9919,7 +9920,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="270" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" s="3">
         <v>10288</v>
       </c>
@@ -9954,7 +9955,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="271" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" s="3">
         <v>10293</v>
       </c>
@@ -9989,7 +9990,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="272" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" s="3">
         <v>10297</v>
       </c>
@@ -10024,7 +10025,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="273" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" s="3">
         <v>10294</v>
       </c>
@@ -10059,7 +10060,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="274" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" s="3">
         <v>10304</v>
       </c>
@@ -10094,7 +10095,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" s="3">
         <v>10317</v>
       </c>
@@ -10129,7 +10130,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="276" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" s="3">
         <v>10318</v>
       </c>
@@ -10164,7 +10165,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="277" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" s="3">
         <v>10322</v>
       </c>
@@ -10199,7 +10200,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" s="3">
         <v>10327</v>
       </c>
@@ -10234,7 +10235,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" s="3">
         <v>10328</v>
       </c>
@@ -10269,7 +10270,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="280" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" s="3">
         <v>10333</v>
       </c>
@@ -10304,7 +10305,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="281" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" s="3">
         <v>10343</v>
       </c>
@@ -10339,7 +10340,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="282" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" s="3">
         <v>10345</v>
       </c>
@@ -10374,7 +10375,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" s="3">
         <v>10349</v>
       </c>
@@ -10409,7 +10410,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" s="3">
         <v>10351</v>
       </c>
@@ -10444,7 +10445,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="285" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" s="3">
         <v>10352</v>
       </c>
@@ -10479,7 +10480,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" s="3">
         <v>10355</v>
       </c>
@@ -10514,7 +10515,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" s="3">
         <v>10356</v>
       </c>
@@ -10549,7 +10550,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" s="3">
         <v>10358</v>
       </c>
@@ -10584,7 +10585,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" s="3">
         <v>10359</v>
       </c>
@@ -10619,7 +10620,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" s="3">
         <v>10360</v>
       </c>
@@ -10654,7 +10655,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" s="3">
         <v>10362</v>
       </c>
@@ -10689,7 +10690,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" s="3">
         <v>10363</v>
       </c>
@@ -10724,7 +10725,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" s="3">
         <v>10364</v>
       </c>
@@ -10759,7 +10760,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" s="3">
         <v>10367</v>
       </c>
@@ -10794,7 +10795,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" s="3">
         <v>10370</v>
       </c>
@@ -10829,7 +10830,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" s="3">
         <v>10371</v>
       </c>
@@ -10864,7 +10865,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" s="3">
         <v>10372</v>
       </c>
@@ -10899,7 +10900,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" s="3">
         <v>10373</v>
       </c>
@@ -10934,7 +10935,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="299" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" s="3">
         <v>10374</v>
       </c>
@@ -10969,7 +10970,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="300" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" s="3">
         <v>10375</v>
       </c>
@@ -11004,7 +11005,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="301" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" s="3">
         <v>10376</v>
       </c>
@@ -11039,7 +11040,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="302" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" s="3">
         <v>10377</v>
       </c>
@@ -11074,7 +11075,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" s="3">
         <v>10381</v>
       </c>
@@ -11109,7 +11110,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" s="3">
         <v>10388</v>
       </c>
@@ -11144,7 +11145,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="305" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" s="3">
         <v>10390</v>
       </c>
@@ -11179,7 +11180,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="306" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" s="3">
         <v>10391</v>
       </c>
@@ -11214,7 +11215,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" s="3">
         <v>10392</v>
       </c>
@@ -11249,7 +11250,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" s="3">
         <v>10394</v>
       </c>
@@ -11284,7 +11285,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" s="3">
         <v>10406</v>
       </c>
@@ -11319,7 +11320,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" s="3">
         <v>10408</v>
       </c>
@@ -11354,7 +11355,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="311" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" s="3">
         <v>10411</v>
       </c>
@@ -11389,7 +11390,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="312" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312" s="3">
         <v>10413</v>
       </c>
@@ -11424,7 +11425,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="313" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" s="3">
         <v>10418</v>
       </c>
@@ -11459,7 +11460,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="314" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" s="3">
         <v>10426</v>
       </c>
@@ -11494,7 +11495,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="315" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" s="3">
         <v>10427</v>
       </c>
@@ -11529,7 +11530,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="316" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316" s="3">
         <v>10428</v>
       </c>
@@ -11564,7 +11565,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" s="3">
         <v>10430</v>
       </c>
@@ -11599,7 +11600,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" s="3">
         <v>10431</v>
       </c>
@@ -11634,7 +11635,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" s="3">
         <v>10440</v>
       </c>
@@ -11669,7 +11670,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" s="3">
         <v>10441</v>
       </c>
@@ -11704,7 +11705,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="321" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" s="3">
         <v>10442</v>
       </c>
@@ -11739,7 +11740,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="322" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322" s="3">
         <v>10443</v>
       </c>
@@ -11774,7 +11775,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="323" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323" s="3">
         <v>10449</v>
       </c>
@@ -11809,7 +11810,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="324" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" s="3">
         <v>10454</v>
       </c>
@@ -11844,7 +11845,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="325" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" s="3">
         <v>10455</v>
       </c>
@@ -11879,7 +11880,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="326" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" s="3">
         <v>10456</v>
       </c>
@@ -11914,7 +11915,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" s="3">
         <v>10457</v>
       </c>
@@ -11949,7 +11950,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" s="3">
         <v>10458</v>
       </c>
@@ -11984,7 +11985,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329" s="3">
         <v>10460</v>
       </c>
@@ -12019,7 +12020,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330" s="3">
         <v>10461</v>
       </c>
@@ -12054,7 +12055,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="331" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331" s="3">
         <v>10462</v>
       </c>
@@ -12089,7 +12090,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="332" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" s="3">
         <v>10463</v>
       </c>
@@ -12124,7 +12125,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="333" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" s="3">
         <v>10468</v>
       </c>
@@ -12159,7 +12160,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="334" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" s="3">
         <v>10469</v>
       </c>
@@ -12194,7 +12195,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="335" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335" s="3">
         <v>10471</v>
       </c>
@@ -12229,7 +12230,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="336" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336" s="3">
         <v>10472</v>
       </c>
@@ -12264,7 +12265,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337" s="3">
         <v>10473</v>
       </c>
@@ -12299,7 +12300,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338" s="3">
         <v>10474</v>
       </c>
@@ -12334,7 +12335,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" s="3">
         <v>10475</v>
       </c>
@@ -12369,7 +12370,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340" s="3">
         <v>10476</v>
       </c>
@@ -12404,7 +12405,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="341" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341" s="3">
         <v>10477</v>
       </c>
@@ -12439,7 +12440,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="342" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342" s="3">
         <v>10478</v>
       </c>
@@ -12474,7 +12475,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="343" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343" s="3">
         <v>10483</v>
       </c>
@@ -12509,7 +12510,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="344" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" s="3">
         <v>10491</v>
       </c>
@@ -12544,7 +12545,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="345" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" s="3">
         <v>10490</v>
       </c>
@@ -12579,7 +12580,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="346" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" s="3">
         <v>10489</v>
       </c>
@@ -12614,7 +12615,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347" s="3">
         <v>10503</v>
       </c>
@@ -12649,7 +12650,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="348" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" s="3">
         <v>10502</v>
       </c>
@@ -12684,7 +12685,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="349" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" s="3">
         <v>10495</v>
       </c>
@@ -12719,7 +12720,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="350" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" s="3">
         <v>10521</v>
       </c>
@@ -12754,7 +12755,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="351" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" s="3">
         <v>10520</v>
       </c>
@@ -12789,7 +12790,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="352" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" s="3">
         <v>10519</v>
       </c>
@@ -12824,7 +12825,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="353" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353" s="3">
         <v>10518</v>
       </c>
@@ -12859,7 +12860,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="354" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" s="3">
         <v>10517</v>
       </c>
@@ -12894,7 +12895,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="355" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355" s="3">
         <v>10516</v>
       </c>
@@ -12929,7 +12930,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="356" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" s="3">
         <v>10515</v>
       </c>
@@ -12964,7 +12965,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="357" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" s="3">
         <v>10509</v>
       </c>
@@ -12999,7 +13000,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="358" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" s="3">
         <v>10507</v>
       </c>
@@ -13034,7 +13035,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="359" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" s="3">
         <v>10541</v>
       </c>
@@ -13069,7 +13070,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="360" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" s="3">
         <v>10536</v>
       </c>
@@ -13104,7 +13105,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="361" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" s="3">
         <v>10535</v>
       </c>
@@ -13139,7 +13140,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="362" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" s="3">
         <v>10534</v>
       </c>
@@ -13174,7 +13175,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="363" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" s="3">
         <v>10533</v>
       </c>
@@ -13209,7 +13210,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="364" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364" s="3">
         <v>10532</v>
       </c>
@@ -13244,7 +13245,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="365" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365" s="3">
         <v>10531</v>
       </c>
@@ -13279,7 +13280,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="366" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366" s="3">
         <v>10530</v>
       </c>
@@ -13314,7 +13315,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="367" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367" s="3">
         <v>10523</v>
       </c>
@@ -13349,7 +13350,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="368" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368" s="3">
         <v>10550</v>
       </c>
@@ -13384,7 +13385,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="369" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369" s="3">
         <v>10549</v>
       </c>
@@ -13419,7 +13420,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="370" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370" s="3">
         <v>10548</v>
       </c>
@@ -13454,7 +13455,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="371" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371" s="3">
         <v>10547</v>
       </c>
@@ -13489,7 +13490,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="372" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372" s="3">
         <v>10551</v>
       </c>
@@ -13524,7 +13525,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="373" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373" s="3">
         <v>10565</v>
       </c>
@@ -13559,7 +13560,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="374" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374" s="3">
         <v>10564</v>
       </c>
@@ -13594,7 +13595,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="375" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375" s="3">
         <v>10576</v>
       </c>
@@ -13629,7 +13630,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="376" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376" s="3">
         <v>10575</v>
       </c>
@@ -13664,7 +13665,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="377" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377" s="3">
         <v>10599</v>
       </c>
@@ -13699,7 +13700,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="378" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378" s="3">
         <v>10598</v>
       </c>
@@ -13734,7 +13735,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="379" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379" s="3">
         <v>10597</v>
       </c>
@@ -13769,7 +13770,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="380" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380" s="3">
         <v>10591</v>
       </c>
@@ -13804,7 +13805,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="381" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381" s="3">
         <v>10581</v>
       </c>
@@ -13839,7 +13840,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="382" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382" s="3">
         <v>10580</v>
       </c>
@@ -13874,7 +13875,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="383" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383" s="3">
         <v>10579</v>
       </c>
@@ -13909,7 +13910,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="384" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384" s="3">
         <v>10578</v>
       </c>
@@ -13944,7 +13945,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="385" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385" s="3">
         <v>10613</v>
       </c>
@@ -13979,7 +13980,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="386" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386" s="3">
         <v>10610</v>
       </c>
@@ -14014,7 +14015,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="387" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387" s="3">
         <v>10600</v>
       </c>
@@ -14049,7 +14050,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="388" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388" s="3">
         <v>10621</v>
       </c>
@@ -14084,7 +14085,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="389" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389" s="3">
         <v>10616</v>
       </c>
@@ -14119,7 +14120,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="390" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390" s="3">
         <v>10614</v>
       </c>
@@ -14154,7 +14155,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="391" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391" s="3">
         <v>10633</v>
       </c>
@@ -14189,7 +14190,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="392" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392" s="3">
         <v>10627</v>
       </c>
@@ -14224,7 +14225,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="393" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393" s="3">
         <v>10626</v>
       </c>
@@ -14259,7 +14260,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="394" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394" s="3">
         <v>10649</v>
       </c>
@@ -14294,7 +14295,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="395" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395" s="3">
         <v>10648</v>
       </c>
@@ -14329,7 +14330,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="396" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396" s="3">
         <v>10647</v>
       </c>
@@ -14364,7 +14365,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="397" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397" s="3">
         <v>10646</v>
       </c>
@@ -14399,7 +14400,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="398" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398" s="3">
         <v>10646</v>
       </c>
@@ -14434,7 +14435,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="399" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399" s="3">
         <v>10645</v>
       </c>
@@ -14469,7 +14470,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="400" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400" s="3">
         <v>10644</v>
       </c>
@@ -14504,7 +14505,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="401" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401" s="3">
         <v>10673</v>
       </c>
@@ -14539,7 +14540,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="402" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402" s="3">
         <v>10672</v>
       </c>
@@ -14574,7 +14575,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="403" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403" s="3">
         <v>10671</v>
       </c>
@@ -14609,7 +14610,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="404" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404" s="3">
         <v>10670</v>
       </c>
@@ -14644,7 +14645,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="405" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405" s="3">
         <v>10669</v>
       </c>
@@ -14679,7 +14680,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="406" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406" s="3">
         <v>10662</v>
       </c>
@@ -14714,7 +14715,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="407" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407" s="3">
         <v>10661</v>
       </c>
@@ -14749,7 +14750,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="408" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408" s="3">
         <v>10659</v>
       </c>
@@ -14784,7 +14785,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="409" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409" s="3">
         <v>10658</v>
       </c>
@@ -14819,7 +14820,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="410" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410" s="3">
         <v>10656</v>
       </c>
@@ -14854,7 +14855,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="411" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411" s="3">
         <v>10655</v>
       </c>
@@ -14889,7 +14890,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="412" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412" s="3">
         <v>10701</v>
       </c>
@@ -14924,7 +14925,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="413" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413" s="3">
         <v>10700</v>
       </c>
@@ -14959,7 +14960,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="414" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414" s="3">
         <v>10696</v>
       </c>
@@ -14994,7 +14995,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="415" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415" s="3">
         <v>10695</v>
       </c>
@@ -15029,7 +15030,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="416" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416" s="3">
         <v>10694</v>
       </c>
@@ -15064,7 +15065,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="417" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417" s="3">
         <v>10693</v>
       </c>
@@ -15099,7 +15100,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="418" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418" s="3">
         <v>10692</v>
       </c>
@@ -15134,7 +15135,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="419" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419" s="3">
         <v>10691</v>
       </c>
@@ -15169,7 +15170,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="420" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420" s="3">
         <v>10690</v>
       </c>
@@ -15204,7 +15205,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="421" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421" s="3">
         <v>10689</v>
       </c>
@@ -15239,7 +15240,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="422" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422" s="3">
         <v>10688</v>
       </c>
@@ -15274,7 +15275,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="423" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423" s="3">
         <v>10687</v>
       </c>
@@ -15309,7 +15310,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="424" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424" s="3">
         <v>10686</v>
       </c>
@@ -15344,7 +15345,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="425" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425" s="3">
         <v>10685</v>
       </c>
@@ -15379,7 +15380,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="426" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426" s="3">
         <v>10684</v>
       </c>
@@ -15414,7 +15415,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="427" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427" s="3">
         <v>10683</v>
       </c>
@@ -15449,7 +15450,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="428" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428" s="3">
         <v>10682</v>
       </c>
@@ -15484,7 +15485,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="429" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429" s="3">
         <v>10716</v>
       </c>
@@ -15519,7 +15520,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="430" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A430" s="3">
         <v>10715</v>
       </c>
@@ -15554,7 +15555,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="431" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431" s="3">
         <v>10711</v>
       </c>
@@ -15589,7 +15590,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="432" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432" s="3">
         <v>10704</v>
       </c>
@@ -15624,7 +15625,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="433" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433" s="3">
         <v>10726</v>
       </c>
@@ -15659,7 +15660,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="434" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434" s="3">
         <v>10725</v>
       </c>
@@ -15694,7 +15695,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="435" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A435" s="3">
         <v>10724</v>
       </c>
@@ -15729,7 +15730,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="436" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A436" s="3">
         <v>10720</v>
       </c>
@@ -15764,7 +15765,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="437" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A437" s="3">
         <v>10719</v>
       </c>
@@ -15799,7 +15800,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="438" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A438" s="3">
         <v>10752</v>
       </c>
@@ -15834,7 +15835,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="439" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A439" s="3">
         <v>10749</v>
       </c>
@@ -15869,7 +15870,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="440" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A440" s="3">
         <v>10748</v>
       </c>
@@ -15904,7 +15905,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="441" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A441" s="3">
         <v>10747</v>
       </c>
@@ -15939,7 +15940,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="442" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A442" s="3">
         <v>10745</v>
       </c>
@@ -15974,7 +15975,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="443" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A443" s="3">
         <v>10744</v>
       </c>
@@ -16009,7 +16010,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="444" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A444" s="3">
         <v>10743</v>
       </c>
@@ -16044,7 +16045,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="445" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A445" s="3">
         <v>10741</v>
       </c>
@@ -16079,7 +16080,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="446" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A446" s="3">
         <v>10739</v>
       </c>
@@ -16114,7 +16115,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="447" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447" s="3">
         <v>10736</v>
       </c>
@@ -16149,7 +16150,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="448" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A448" s="3">
         <v>10735</v>
       </c>
@@ -16184,7 +16185,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="449" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A449" s="3">
         <v>10734</v>
       </c>
@@ -16219,7 +16220,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="450" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A450" s="3">
         <v>10733</v>
       </c>
@@ -16254,7 +16255,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="451" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A451" s="3">
         <v>10732</v>
       </c>
@@ -16289,7 +16290,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="452" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A452" s="3">
         <v>10732</v>
       </c>
@@ -16324,7 +16325,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="453" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A453" s="3">
         <v>10781</v>
       </c>
@@ -16359,7 +16360,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="454" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A454" s="3">
         <v>10780</v>
       </c>
@@ -16394,7 +16395,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="455" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A455" s="3">
         <v>10779</v>
       </c>
@@ -16429,7 +16430,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="456" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A456" s="3">
         <v>10778</v>
       </c>
@@ -16464,7 +16465,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="457" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A457" s="3">
         <v>10777</v>
       </c>
@@ -16499,7 +16500,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="458" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A458" s="3">
         <v>10776</v>
       </c>
@@ -16534,7 +16535,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="459" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A459" s="3">
         <v>10775</v>
       </c>
@@ -16569,7 +16570,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="460" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A460" s="3">
         <v>10774</v>
       </c>
@@ -16604,7 +16605,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="461" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461" s="3">
         <v>10773</v>
       </c>
@@ -16639,7 +16640,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="462" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A462" s="3">
         <v>10772</v>
       </c>
@@ -16674,7 +16675,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="463" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A463" s="3">
         <v>10771</v>
       </c>
@@ -16709,7 +16710,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="464" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A464" s="3">
         <v>10768</v>
       </c>
@@ -16744,7 +16745,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="465" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A465" s="3">
         <v>10767</v>
       </c>
@@ -16779,7 +16780,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="466" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A466" s="3">
         <v>10766</v>
       </c>
@@ -16814,7 +16815,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="467" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A467" s="3">
         <v>10765</v>
       </c>
@@ -16849,7 +16850,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="468" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A468" s="3">
         <v>10764</v>
       </c>
@@ -16884,7 +16885,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="469" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A469" s="3">
         <v>10763</v>
       </c>
@@ -16919,7 +16920,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="470" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A470" s="3">
         <v>10762</v>
       </c>
@@ -16954,7 +16955,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="471" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A471" s="3">
         <v>10761</v>
       </c>
@@ -16989,7 +16990,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="472" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A472" s="3">
         <v>10760</v>
       </c>
@@ -17024,7 +17025,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="473" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A473" s="3">
         <v>10759</v>
       </c>
@@ -17059,7 +17060,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="474" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A474" s="3">
         <v>10758</v>
       </c>
@@ -17094,7 +17095,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="475" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A475" s="3">
         <v>10756</v>
       </c>
@@ -17129,7 +17130,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="476" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A476" s="3">
         <v>10791</v>
       </c>
@@ -17164,7 +17165,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="477" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A477" s="3">
         <v>10788</v>
       </c>
@@ -17199,7 +17200,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="478" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A478" s="3">
         <v>10799</v>
       </c>
@@ -17234,7 +17235,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="479" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A479" s="3">
         <v>10800</v>
       </c>
@@ -17269,7 +17270,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="480" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A480" s="3">
         <v>10817</v>
       </c>
@@ -17304,7 +17305,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="481" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A481" s="3">
         <v>10819</v>
       </c>
@@ -17339,7 +17340,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="482" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A482" s="3">
         <v>10820</v>
       </c>
@@ -17374,7 +17375,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="483" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A483" s="3">
         <v>10821</v>
       </c>
@@ -17409,7 +17410,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="484" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A484" s="3">
         <v>10822</v>
       </c>
@@ -17444,7 +17445,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="485" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A485" s="3">
         <v>10823</v>
       </c>
@@ -17479,7 +17480,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="486" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A486" s="3">
         <v>10825</v>
       </c>
@@ -17514,7 +17515,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="487" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A487" s="3">
         <v>10826</v>
       </c>
@@ -17549,7 +17550,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="488" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A488" s="3">
         <v>10827</v>
       </c>
@@ -17584,7 +17585,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="489" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A489" s="3">
         <v>10828</v>
       </c>
@@ -17619,7 +17620,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="490" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A490" s="3">
         <v>10831</v>
       </c>
@@ -17654,7 +17655,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="491" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A491" s="3">
         <v>10832</v>
       </c>
@@ -17689,7 +17690,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="492" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A492" s="3">
         <v>10833</v>
       </c>
@@ -17724,7 +17725,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="493" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A493" s="3">
         <v>10838</v>
       </c>
@@ -17759,7 +17760,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="494" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A494" s="3">
         <v>10839</v>
       </c>
@@ -17794,7 +17795,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="495" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A495" s="3">
         <v>10840</v>
       </c>
@@ -17829,7 +17830,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="496" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A496" s="3">
         <v>10843</v>
       </c>
@@ -17864,7 +17865,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="497" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A497" s="3">
         <v>10845</v>
       </c>
@@ -17899,7 +17900,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="498" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A498" s="3">
         <v>10846</v>
       </c>
@@ -17934,7 +17935,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="499" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A499" s="3">
         <v>10848</v>
       </c>
@@ -17969,7 +17970,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="500" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A500" s="3">
         <v>10849</v>
       </c>
@@ -18004,7 +18005,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="501" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A501" s="3">
         <v>10850</v>
       </c>
@@ -18039,7 +18040,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="502" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A502" s="3">
         <v>10851</v>
       </c>
@@ -18074,7 +18075,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="503" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A503" s="3">
         <v>10852</v>
       </c>
@@ -18109,7 +18110,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="504" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A504" s="3">
         <v>10860</v>
       </c>
@@ -18144,7 +18145,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="505" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A505" s="3">
         <v>10861</v>
       </c>
@@ -18179,7 +18180,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="506" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A506" s="3">
         <v>10862</v>
       </c>
@@ -18214,7 +18215,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="507" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A507" s="3">
         <v>10864</v>
       </c>
@@ -18249,7 +18250,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="508" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A508" s="3">
         <v>10866</v>
       </c>
@@ -18284,7 +18285,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="509" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A509" s="3">
         <v>10869</v>
       </c>
@@ -18319,7 +18320,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="510" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A510" s="3">
         <v>10870</v>
       </c>
@@ -18354,7 +18355,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="511" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A511" s="3">
         <v>10871</v>
       </c>
@@ -18389,7 +18390,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="512" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A512" s="3">
         <v>10872</v>
       </c>
@@ -18424,7 +18425,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="513" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A513" s="3">
         <v>10873</v>
       </c>
@@ -18459,7 +18460,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="514" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A514" s="3">
         <v>10874</v>
       </c>
@@ -18494,7 +18495,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="515" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A515" s="3">
         <v>10881</v>
       </c>
@@ -18529,7 +18530,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="516" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A516" s="3">
         <v>10882</v>
       </c>
@@ -18564,7 +18565,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="517" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A517" s="3">
         <v>10883</v>
       </c>
@@ -18599,7 +18600,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="518" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A518" s="3">
         <v>10887</v>
       </c>
@@ -18634,7 +18635,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="519" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A519" s="3">
         <v>10888</v>
       </c>
@@ -18669,7 +18670,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="520" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A520" s="3">
         <v>10889</v>
       </c>
@@ -18704,7 +18705,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="521" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A521" s="3">
         <v>10894</v>
       </c>
@@ -18739,7 +18740,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="522" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A522" s="3">
         <v>10899</v>
       </c>
@@ -18774,7 +18775,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="523" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A523" s="3">
         <v>10900</v>
       </c>
@@ -18809,7 +18810,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="524" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A524" s="3">
         <v>10901</v>
       </c>
@@ -18844,7 +18845,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="525" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A525" s="3">
         <v>10902</v>
       </c>
@@ -18879,7 +18880,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="526" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A526" s="3">
         <v>10903</v>
       </c>
@@ -18914,7 +18915,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="527" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A527" s="3">
         <v>10904</v>
       </c>
@@ -18949,7 +18950,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="528" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A528" s="3">
         <v>10905</v>
       </c>
@@ -18984,7 +18985,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="529" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A529" s="3">
         <v>10906</v>
       </c>
@@ -19019,7 +19020,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="530" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A530" s="3">
         <v>10907</v>
       </c>
@@ -19054,7 +19055,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="531" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A531" s="3">
         <v>10908</v>
       </c>
@@ -19089,7 +19090,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="532" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A532" s="3">
         <v>10910</v>
       </c>
@@ -19124,7 +19125,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="533" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A533" s="3">
         <v>10913</v>
       </c>
@@ -19159,7 +19160,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="534" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A534" s="3">
         <v>10914</v>
       </c>
@@ -19194,7 +19195,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="535" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A535" s="3">
         <v>10915</v>
       </c>
@@ -19229,7 +19230,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="536" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A536" s="3">
         <v>10918</v>
       </c>
@@ -19264,7 +19265,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="537" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A537" s="3">
         <v>10919</v>
       </c>
@@ -19299,7 +19300,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="538" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A538" s="3">
         <v>10920</v>
       </c>
@@ -19334,7 +19335,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="539" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A539" s="3">
         <v>10927</v>
       </c>
@@ -19369,7 +19370,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="540" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A540" s="3">
         <v>10928</v>
       </c>
@@ -19404,7 +19405,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="541" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A541" s="3">
         <v>10931</v>
       </c>
@@ -19439,7 +19440,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="542" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A542" s="3">
         <v>10932</v>
       </c>
@@ -19474,7 +19475,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="543" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A543" s="3">
         <v>10933</v>
       </c>
@@ -19509,7 +19510,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="544" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A544" s="3">
         <v>10935</v>
       </c>
@@ -19544,7 +19545,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="545" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A545" s="3">
         <v>10939</v>
       </c>
@@ -19579,7 +19580,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="546" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A546" s="3">
         <v>10941</v>
       </c>
@@ -19614,7 +19615,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="547" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A547" s="3">
         <v>10942</v>
       </c>
@@ -19649,7 +19650,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="548" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A548" s="3">
         <v>10943</v>
       </c>
@@ -19684,7 +19685,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="549" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A549" s="3">
         <v>10944</v>
       </c>
@@ -19719,7 +19720,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="550" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A550" s="3">
         <v>10945</v>
       </c>
@@ -19754,7 +19755,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="551" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A551" s="3">
         <v>10946</v>
       </c>
@@ -19789,7 +19790,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="552" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A552" s="3">
         <v>10947</v>
       </c>
@@ -19824,7 +19825,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="553" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A553" s="3">
         <v>10948</v>
       </c>
@@ -19859,7 +19860,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="554" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A554" s="3">
         <v>10949</v>
       </c>
@@ -19894,7 +19895,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="555" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A555" s="3">
         <v>10950</v>
       </c>
@@ -19929,7 +19930,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="556" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A556" s="3">
         <v>10951</v>
       </c>
@@ -19964,7 +19965,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="557" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A557" s="3">
         <v>10954</v>
       </c>
@@ -19999,7 +20000,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="558" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A558" s="3">
         <v>10960</v>
       </c>
@@ -20034,7 +20035,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="559" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A559" s="3">
         <v>10964</v>
       </c>
@@ -20069,7 +20070,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="560" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A560" s="3">
         <v>10965</v>
       </c>
@@ -20104,7 +20105,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="561" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A561" s="3">
         <v>10966</v>
       </c>
@@ -20139,7 +20140,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="562" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A562" s="3">
         <v>10967</v>
       </c>
@@ -20174,7 +20175,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="563" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A563" s="3">
         <v>10969</v>
       </c>
@@ -20209,7 +20210,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="564" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A564" s="3">
         <v>10970</v>
       </c>
@@ -20244,7 +20245,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="565" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A565" s="3">
         <v>10972</v>
       </c>
@@ -20279,7 +20280,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="566" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A566" s="3">
         <v>10982</v>
       </c>
@@ -20314,7 +20315,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="567" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A567" s="3">
         <v>10983</v>
       </c>
@@ -20349,7 +20350,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="568" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A568" s="3">
         <v>10984</v>
       </c>
@@ -20384,7 +20385,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="569" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A569" s="3">
         <v>10985</v>
       </c>
@@ -20419,7 +20420,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="570" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A570" s="3">
         <v>10986</v>
       </c>
@@ -20454,7 +20455,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="571" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A571" s="3">
         <v>10987</v>
       </c>
@@ -20489,7 +20490,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="572" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A572" s="3">
         <v>10988</v>
       </c>
@@ -20524,7 +20525,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="573" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A573" s="3">
         <v>10989</v>
       </c>
@@ -20559,7 +20560,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="574" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A574" s="3">
         <v>10967</v>
       </c>
@@ -20594,7 +20595,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="575" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A575" s="3">
         <v>10996</v>
       </c>
@@ -20629,7 +20630,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="576" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A576" s="3">
         <v>10998</v>
       </c>
@@ -20664,7 +20665,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="577" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A577" s="3">
         <v>11000</v>
       </c>
@@ -20699,7 +20700,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="578" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A578" s="3">
         <v>11001</v>
       </c>
@@ -20734,7 +20735,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="579" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A579" s="3">
         <v>11002</v>
       </c>
@@ -20769,7 +20770,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="580" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A580" s="3">
         <v>11003</v>
       </c>
@@ -20804,7 +20805,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="581" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A581" s="3">
         <v>11006</v>
       </c>
@@ -20839,7 +20840,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="582" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A582" s="3">
         <v>11007</v>
       </c>
@@ -20874,7 +20875,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="583" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A583" s="3">
         <v>11008</v>
       </c>
@@ -20909,7 +20910,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="584" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A584" s="3">
         <v>11009</v>
       </c>
@@ -20944,7 +20945,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="585" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A585" s="3">
         <v>11013</v>
       </c>
@@ -20979,7 +20980,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="586" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A586" s="3">
         <v>11014</v>
       </c>
@@ -21014,7 +21015,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="587" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A587" s="3">
         <v>11015</v>
       </c>
@@ -21049,7 +21050,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="588" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A588" s="3">
         <v>11017</v>
       </c>
@@ -21084,7 +21085,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="589" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A589" s="3">
         <v>11018</v>
       </c>
@@ -21119,7 +21120,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="590" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A590" s="3">
         <v>11023</v>
       </c>
@@ -21154,7 +21155,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="591" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A591" s="3">
         <v>11024</v>
       </c>
@@ -21189,7 +21190,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="592" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A592" s="3">
         <v>11027</v>
       </c>
@@ -21224,7 +21225,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="593" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A593" s="3">
         <v>11028</v>
       </c>
@@ -21259,7 +21260,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="594" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A594" s="3">
         <v>11036</v>
       </c>
@@ -21294,7 +21295,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="595" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A595" s="3">
         <v>11037</v>
       </c>
@@ -21329,7 +21330,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="596" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A596" s="3">
         <v>11041</v>
       </c>
@@ -21364,7 +21365,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="597" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A597" s="3">
         <v>11043</v>
       </c>
@@ -21399,7 +21400,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="598" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A598" s="3">
         <v>11044</v>
       </c>
@@ -21434,7 +21435,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="599" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A599" s="3">
         <v>11045</v>
       </c>
@@ -21469,7 +21470,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="600" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A600" s="3">
         <v>11046</v>
       </c>
@@ -21504,7 +21505,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="601" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A601" s="3">
         <v>11047</v>
       </c>
@@ -21539,7 +21540,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="602" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A602" s="3">
         <v>11053</v>
       </c>
@@ -21574,7 +21575,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="603" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A603" s="3">
         <v>11056</v>
       </c>
@@ -21609,7 +21610,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="604" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A604" s="3">
         <v>11057</v>
       </c>
@@ -21644,7 +21645,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="605" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A605" s="3">
         <v>11058</v>
       </c>
@@ -21679,7 +21680,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="606" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A606" s="3">
         <v>11059</v>
       </c>
@@ -21714,7 +21715,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="607" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A607" s="3">
         <v>11060</v>
       </c>
@@ -21749,7 +21750,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="608" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A608" s="3">
         <v>11061</v>
       </c>
@@ -21784,7 +21785,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="609" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A609" s="3">
         <v>11062</v>
       </c>
@@ -21819,7 +21820,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="610" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A610" s="3">
         <v>11063</v>
       </c>
@@ -21854,7 +21855,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="611" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A611" s="3">
         <v>11064</v>
       </c>
@@ -21889,7 +21890,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="612" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A612" s="3">
         <v>11065</v>
       </c>
@@ -21924,7 +21925,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="613" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A613" s="3">
         <v>11072</v>
       </c>
@@ -21959,7 +21960,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="614" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A614" s="3">
         <v>11073</v>
       </c>
@@ -21994,7 +21995,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="615" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A615" s="3">
         <v>11076</v>
       </c>
@@ -22029,7 +22030,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="616" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A616" s="3">
         <v>11077</v>
       </c>
@@ -22064,7 +22065,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="617" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A617" s="3">
         <v>11078</v>
       </c>
@@ -22099,7 +22100,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="618" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A618" s="3">
         <v>11081</v>
       </c>
@@ -22134,7 +22135,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="619" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A619" s="3">
         <v>11083</v>
       </c>
@@ -22169,7 +22170,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="620" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A620" s="3">
         <v>11084</v>
       </c>
@@ -22204,7 +22205,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="621" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A621" s="3">
         <v>11085</v>
       </c>
@@ -22239,7 +22240,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="622" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A622" s="3">
         <v>11095</v>
       </c>
@@ -22274,7 +22275,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="623" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A623" s="3">
         <v>11100</v>
       </c>
@@ -22309,7 +22310,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="624" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A624" s="3">
         <v>11099</v>
       </c>
@@ -22344,7 +22345,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="625" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A625" s="3">
         <v>11093</v>
       </c>
@@ -22460,7 +22461,7 @@
         <v>18</v>
       </c>
       <c r="D628" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E628" s="3" t="s">
         <v>23</v>
@@ -26798,9 +26799,7 @@
       <c r="F752" s="3"/>
       <c r="G752" s="4"/>
       <c r="H752" s="4"/>
-      <c r="I752" s="3" t="s">
-        <v>25</v>
-      </c>
+      <c r="I752" s="3"/>
       <c r="J752" s="5"/>
       <c r="K752" s="3"/>
     </row>
@@ -26813,9 +26812,7 @@
       <c r="F753" s="3"/>
       <c r="G753" s="4"/>
       <c r="H753" s="4"/>
-      <c r="I753" s="3" t="s">
-        <v>25</v>
-      </c>
+      <c r="I753" s="3"/>
       <c r="J753" s="5"/>
       <c r="K753" s="3"/>
     </row>
@@ -30084,6 +30081,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A3:K753" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="6">
+      <filters blank="1">
+        <dateGroupItem year="2026" month="7" dateTimeGrouping="month"/>
+      </filters>
+    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:K753">
       <sortCondition ref="I3:I753"/>
     </sortState>

--- a/PCM_OS_Intranet.xlsx
+++ b/PCM_OS_Intranet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jasmine\Desktop\PCM-Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84B8F9E2-D475-4A3F-80AC-18E72E1A022B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67EFED4D-B131-4A21-8484-E28817C7F8D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -540,7 +540,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:K1004"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -610,7 +609,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>9576</v>
       </c>
@@ -645,7 +644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>9571</v>
       </c>
@@ -680,7 +679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>9571</v>
       </c>
@@ -715,7 +714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>9598</v>
       </c>
@@ -750,7 +749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>9713</v>
       </c>
@@ -785,7 +784,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>9722</v>
       </c>
@@ -820,7 +819,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>9418</v>
       </c>
@@ -855,7 +854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>10306</v>
       </c>
@@ -890,7 +889,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>10470</v>
       </c>
@@ -925,7 +924,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>10588</v>
       </c>
@@ -960,7 +959,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>10650</v>
       </c>
@@ -995,7 +994,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>9547</v>
       </c>
@@ -1030,7 +1029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>9667</v>
       </c>
@@ -1065,7 +1064,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>9750</v>
       </c>
@@ -1100,7 +1099,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>9995</v>
       </c>
@@ -1135,7 +1134,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>9486</v>
       </c>
@@ -1170,7 +1169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>9540</v>
       </c>
@@ -1205,7 +1204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>10220</v>
       </c>
@@ -1240,7 +1239,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>10344</v>
       </c>
@@ -1275,7 +1274,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>10459</v>
       </c>
@@ -1310,7 +1309,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>9595</v>
       </c>
@@ -1345,7 +1344,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>9597</v>
       </c>
@@ -1380,7 +1379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>9623</v>
       </c>
@@ -1415,7 +1414,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>10306</v>
       </c>
@@ -1450,7 +1449,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>10507</v>
       </c>
@@ -1485,7 +1484,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>10582</v>
       </c>
@@ -1520,7 +1519,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>10657</v>
       </c>
@@ -1555,7 +1554,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>10728</v>
       </c>
@@ -1590,7 +1589,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>10824</v>
       </c>
@@ -1625,7 +1624,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>10909</v>
       </c>
@@ -1660,7 +1659,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>11079</v>
       </c>
@@ -1695,7 +1694,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>9463</v>
       </c>
@@ -1730,7 +1729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>9488</v>
       </c>
@@ -1765,7 +1764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>9485</v>
       </c>
@@ -1800,7 +1799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>9481</v>
       </c>
@@ -1835,7 +1834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>9491</v>
       </c>
@@ -1870,7 +1869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>9519</v>
       </c>
@@ -1905,7 +1904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>9531</v>
       </c>
@@ -1940,7 +1939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <v>9541</v>
       </c>
@@ -1975,7 +1974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>9570</v>
       </c>
@@ -2010,7 +2009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <v>9569</v>
       </c>
@@ -2045,7 +2044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <v>9562</v>
       </c>
@@ -2080,7 +2079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
         <v>9561</v>
       </c>
@@ -2115,7 +2114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <v>9560</v>
       </c>
@@ -2150,7 +2149,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <v>9587</v>
       </c>
@@ -2185,7 +2184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <v>9600</v>
       </c>
@@ -2220,7 +2219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
         <v>9599</v>
       </c>
@@ -2255,7 +2254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <v>9605</v>
       </c>
@@ -2290,7 +2289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
         <v>9616</v>
       </c>
@@ -2325,7 +2324,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
         <v>9618</v>
       </c>
@@ -2360,7 +2359,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
         <v>9625</v>
       </c>
@@ -2395,7 +2394,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
         <v>9629</v>
       </c>
@@ -2430,7 +2429,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
         <v>9631</v>
       </c>
@@ -2465,7 +2464,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
         <v>9632</v>
       </c>
@@ -2500,7 +2499,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
         <v>9633</v>
       </c>
@@ -2535,7 +2534,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
         <v>9636</v>
       </c>
@@ -2570,7 +2569,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
         <v>9637</v>
       </c>
@@ -2605,7 +2604,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
         <v>9640</v>
       </c>
@@ -2640,7 +2639,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
         <v>9652</v>
       </c>
@@ -2675,7 +2674,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
         <v>9662</v>
       </c>
@@ -2710,7 +2709,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
         <v>9666</v>
       </c>
@@ -2745,7 +2744,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
         <v>9670</v>
       </c>
@@ -2780,7 +2779,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
         <v>9676</v>
       </c>
@@ -2815,7 +2814,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
         <v>9678</v>
       </c>
@@ -2850,7 +2849,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
         <v>9681</v>
       </c>
@@ -2885,7 +2884,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
         <v>9682</v>
       </c>
@@ -2920,7 +2919,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" s="3">
         <v>9686</v>
       </c>
@@ -2955,7 +2954,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
         <v>9689</v>
       </c>
@@ -2990,7 +2989,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" s="3">
         <v>9692</v>
       </c>
@@ -3025,7 +3024,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
         <v>9693</v>
       </c>
@@ -3060,7 +3059,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
         <v>9698</v>
       </c>
@@ -3095,7 +3094,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" s="3">
         <v>9709</v>
       </c>
@@ -3130,7 +3129,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" s="3">
         <v>9710</v>
       </c>
@@ -3165,7 +3164,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" s="3">
         <v>9711</v>
       </c>
@@ -3200,7 +3199,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
         <v>9723</v>
       </c>
@@ -3235,7 +3234,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
         <v>9744</v>
       </c>
@@ -3270,7 +3269,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
         <v>9790</v>
       </c>
@@ -3305,7 +3304,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
         <v>9922</v>
       </c>
@@ -3340,7 +3339,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" s="3">
         <v>9981</v>
       </c>
@@ -3375,7 +3374,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
         <v>9986</v>
       </c>
@@ -3410,7 +3409,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
         <v>10011</v>
       </c>
@@ -3445,7 +3444,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85" s="3">
         <v>10163</v>
       </c>
@@ -3480,7 +3479,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86" s="3">
         <v>10242</v>
       </c>
@@ -3515,7 +3514,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
         <v>10334</v>
       </c>
@@ -3550,7 +3549,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="88" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88" s="3">
         <v>10357</v>
       </c>
@@ -3585,7 +3584,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
         <v>10357</v>
       </c>
@@ -3620,7 +3619,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90" s="3">
         <v>10368</v>
       </c>
@@ -3655,7 +3654,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
         <v>10611</v>
       </c>
@@ -3690,7 +3689,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92" s="3">
         <v>10699</v>
       </c>
@@ -3725,7 +3724,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93" s="3">
         <v>10679</v>
       </c>
@@ -3760,7 +3759,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94" s="3">
         <v>10703</v>
       </c>
@@ -3795,7 +3794,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A95" s="3">
         <v>10713</v>
       </c>
@@ -3830,7 +3829,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96" s="3">
         <v>9390</v>
       </c>
@@ -3865,7 +3864,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" s="3">
         <v>9389</v>
       </c>
@@ -3900,7 +3899,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" s="3">
         <v>9388</v>
       </c>
@@ -3935,7 +3934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99" s="3">
         <v>9406</v>
       </c>
@@ -3970,7 +3969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100" s="3">
         <v>9405</v>
       </c>
@@ -4005,7 +4004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" s="3">
         <v>9404</v>
       </c>
@@ -4040,7 +4039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102" s="3">
         <v>9401</v>
       </c>
@@ -4075,7 +4074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103" s="3">
         <v>9400</v>
       </c>
@@ -4110,7 +4109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104" s="3">
         <v>9398</v>
       </c>
@@ -4145,7 +4144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105" s="3">
         <v>9397</v>
       </c>
@@ -4180,7 +4179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106" s="3">
         <v>9396</v>
       </c>
@@ -4215,7 +4214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107" s="3">
         <v>9416</v>
       </c>
@@ -4250,7 +4249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108" s="3">
         <v>9414</v>
       </c>
@@ -4285,7 +4284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109" s="3">
         <v>9417</v>
       </c>
@@ -4320,7 +4319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A110" s="3">
         <v>9437</v>
       </c>
@@ -4355,7 +4354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A111" s="3">
         <v>9436</v>
       </c>
@@ -4390,7 +4389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112" s="3">
         <v>9435</v>
       </c>
@@ -4425,7 +4424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A113" s="3">
         <v>9440</v>
       </c>
@@ -4460,7 +4459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A114" s="3">
         <v>9447</v>
       </c>
@@ -4495,7 +4494,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A115" s="3">
         <v>9460</v>
       </c>
@@ -4530,7 +4529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A116" s="3">
         <v>9459</v>
       </c>
@@ -4565,7 +4564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A117" s="3">
         <v>9451</v>
       </c>
@@ -4600,7 +4599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A118" s="3">
         <v>9465</v>
       </c>
@@ -4635,7 +4634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A119" s="3">
         <v>9464</v>
       </c>
@@ -4670,7 +4669,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A120" s="3">
         <v>9462</v>
       </c>
@@ -4705,7 +4704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A121" s="3">
         <v>9487</v>
       </c>
@@ -4740,7 +4739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A122" s="3">
         <v>9484</v>
       </c>
@@ -4775,7 +4774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A123" s="3">
         <v>9482</v>
       </c>
@@ -4810,7 +4809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A124" s="3">
         <v>9480</v>
       </c>
@@ -4845,7 +4844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A125" s="3">
         <v>9490</v>
       </c>
@@ -4880,7 +4879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A126" s="3">
         <v>9501</v>
       </c>
@@ -4915,7 +4914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A127" s="3">
         <v>9502</v>
       </c>
@@ -4950,7 +4949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A128" s="3">
         <v>9520</v>
       </c>
@@ -4985,7 +4984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A129" s="3">
         <v>9516</v>
       </c>
@@ -5020,7 +5019,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A130" s="3">
         <v>9515</v>
       </c>
@@ -5055,7 +5054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A131" s="3">
         <v>9514</v>
       </c>
@@ -5090,7 +5089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A132" s="3">
         <v>9513</v>
       </c>
@@ -5125,7 +5124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A133" s="3">
         <v>9512</v>
       </c>
@@ -5160,7 +5159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A134" s="3">
         <v>9510</v>
       </c>
@@ -5195,7 +5194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A135" s="3">
         <v>9524</v>
       </c>
@@ -5230,7 +5229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A136" s="3">
         <v>9523</v>
       </c>
@@ -5265,7 +5264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A137" s="3">
         <v>9539</v>
       </c>
@@ -5300,7 +5299,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A138" s="3">
         <v>9538</v>
       </c>
@@ -5335,7 +5334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A139" s="3">
         <v>9549</v>
       </c>
@@ -5370,7 +5369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A140" s="3">
         <v>9553</v>
       </c>
@@ -5405,7 +5404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A141" s="3">
         <v>9551</v>
       </c>
@@ -5440,7 +5439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A142" s="3">
         <v>9554</v>
       </c>
@@ -5475,7 +5474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A143" s="3">
         <v>9575</v>
       </c>
@@ -5510,7 +5509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A144" s="3">
         <v>9574</v>
       </c>
@@ -5545,7 +5544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A145" s="3">
         <v>9568</v>
       </c>
@@ -5580,7 +5579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A146" s="3">
         <v>9588</v>
       </c>
@@ -5615,7 +5614,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A147" s="3">
         <v>9586</v>
       </c>
@@ -5650,7 +5649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A148" s="3">
         <v>9585</v>
       </c>
@@ -5685,7 +5684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A149" s="3">
         <v>9584</v>
       </c>
@@ -5720,7 +5719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A150" s="3">
         <v>9582</v>
       </c>
@@ -5755,7 +5754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A151" s="3">
         <v>9580</v>
       </c>
@@ -5790,7 +5789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A152" s="3">
         <v>9579</v>
       </c>
@@ -5825,7 +5824,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A153" s="3">
         <v>9578</v>
       </c>
@@ -5860,7 +5859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A154" s="3">
         <v>9596</v>
       </c>
@@ -5895,7 +5894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A155" s="3">
         <v>9606</v>
       </c>
@@ -5930,7 +5929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A156" s="3">
         <v>9614</v>
       </c>
@@ -5965,7 +5964,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="157" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A157" s="3">
         <v>9619</v>
       </c>
@@ -6000,7 +5999,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="158" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A158" s="3">
         <v>9620</v>
       </c>
@@ -6035,7 +6034,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="159" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A159" s="3">
         <v>9622</v>
       </c>
@@ -6070,7 +6069,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="160" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A160" s="3">
         <v>9639</v>
       </c>
@@ -6105,7 +6104,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="161" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A161" s="3">
         <v>9641</v>
       </c>
@@ -6140,7 +6139,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A162" s="3">
         <v>9642</v>
       </c>
@@ -6175,7 +6174,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="163" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A163" s="3">
         <v>9648</v>
       </c>
@@ -6210,7 +6209,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="164" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A164" s="3">
         <v>9654</v>
       </c>
@@ -6245,7 +6244,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="165" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A165" s="3">
         <v>9663</v>
       </c>
@@ -6280,7 +6279,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="166" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A166" s="3">
         <v>9669</v>
       </c>
@@ -6315,7 +6314,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="167" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A167" s="3">
         <v>9672</v>
       </c>
@@ -6350,7 +6349,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="168" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A168" s="3">
         <v>9677</v>
       </c>
@@ -6385,7 +6384,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="169" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A169" s="3">
         <v>9679</v>
       </c>
@@ -6420,7 +6419,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="170" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A170" s="3">
         <v>9680</v>
       </c>
@@ -6455,7 +6454,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="171" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A171" s="3">
         <v>9684</v>
       </c>
@@ -6490,7 +6489,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A172" s="3">
         <v>9688</v>
       </c>
@@ -6525,7 +6524,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="173" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A173" s="3">
         <v>9690</v>
       </c>
@@ -6560,7 +6559,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="174" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A174" s="3">
         <v>9691</v>
       </c>
@@ -6595,7 +6594,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="175" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A175" s="3">
         <v>9701</v>
       </c>
@@ -6630,7 +6629,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="176" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A176" s="3">
         <v>9702</v>
       </c>
@@ -6665,7 +6664,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="177" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A177" s="3">
         <v>9703</v>
       </c>
@@ -6700,7 +6699,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="178" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A178" s="3">
         <v>9704</v>
       </c>
@@ -6735,7 +6734,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="179" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A179" s="3">
         <v>9705</v>
       </c>
@@ -6770,7 +6769,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="180" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A180" s="3">
         <v>9706</v>
       </c>
@@ -6805,7 +6804,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="181" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A181" s="3">
         <v>9715</v>
       </c>
@@ -6840,7 +6839,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="182" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A182" s="3">
         <v>9716</v>
       </c>
@@ -6875,7 +6874,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="183" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A183" s="3">
         <v>9719</v>
       </c>
@@ -6910,7 +6909,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="184" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A184" s="3">
         <v>9721</v>
       </c>
@@ -6945,7 +6944,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="185" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A185" s="3">
         <v>9726</v>
       </c>
@@ -6980,7 +6979,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="186" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A186" s="3">
         <v>9729</v>
       </c>
@@ -7015,7 +7014,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="187" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A187" s="3">
         <v>9732</v>
       </c>
@@ -7050,7 +7049,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="188" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A188" s="3">
         <v>9733</v>
       </c>
@@ -7085,7 +7084,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="189" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A189" s="3">
         <v>9734</v>
       </c>
@@ -7120,7 +7119,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="190" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A190" s="3">
         <v>9735</v>
       </c>
@@ -7155,7 +7154,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="191" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A191" s="3">
         <v>9738</v>
       </c>
@@ -7190,7 +7189,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="192" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A192" s="3">
         <v>9739</v>
       </c>
@@ -7225,7 +7224,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="193" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A193" s="3">
         <v>9741</v>
       </c>
@@ -7260,7 +7259,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="194" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A194" s="3">
         <v>9742</v>
       </c>
@@ -7295,7 +7294,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="195" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A195" s="3">
         <v>9745</v>
       </c>
@@ -7330,7 +7329,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="196" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A196" s="3">
         <v>9749</v>
       </c>
@@ -7365,7 +7364,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="197" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A197" s="3">
         <v>9751</v>
       </c>
@@ -7400,7 +7399,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="198" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A198" s="3">
         <v>9754</v>
       </c>
@@ -7435,7 +7434,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="199" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A199" s="3">
         <v>9755</v>
       </c>
@@ -7470,7 +7469,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="200" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A200" s="3">
         <v>9756</v>
       </c>
@@ -7505,7 +7504,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="201" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A201" s="3">
         <v>9757</v>
       </c>
@@ -7540,7 +7539,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="202" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A202" s="3">
         <v>9758</v>
       </c>
@@ -7575,7 +7574,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="203" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A203" s="3">
         <v>9759</v>
       </c>
@@ -7610,7 +7609,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="204" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A204" s="3">
         <v>9810</v>
       </c>
@@ -7645,7 +7644,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="205" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A205" s="3">
         <v>9816</v>
       </c>
@@ -7680,7 +7679,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="206" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A206" s="3">
         <v>9818</v>
       </c>
@@ -7715,7 +7714,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="207" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A207" s="3">
         <v>9828</v>
       </c>
@@ -7750,7 +7749,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="208" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A208" s="3">
         <v>9829</v>
       </c>
@@ -7785,7 +7784,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="209" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A209" s="3">
         <v>9876</v>
       </c>
@@ -7820,7 +7819,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="210" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A210" s="3">
         <v>9875</v>
       </c>
@@ -7855,7 +7854,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="211" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A211" s="3">
         <v>9874</v>
       </c>
@@ -7890,7 +7889,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="212" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A212" s="3">
         <v>9873</v>
       </c>
@@ -7925,7 +7924,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="213" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A213" s="3">
         <v>9857</v>
       </c>
@@ -7960,7 +7959,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="214" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A214" s="3">
         <v>9856</v>
       </c>
@@ -7995,7 +7994,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="215" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A215" s="3">
         <v>9854</v>
       </c>
@@ -8030,7 +8029,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="216" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A216" s="3">
         <v>9850</v>
       </c>
@@ -8065,7 +8064,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="217" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A217" s="3">
         <v>9843</v>
       </c>
@@ -8100,7 +8099,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="218" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A218" s="3">
         <v>9842</v>
       </c>
@@ -8135,7 +8134,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="219" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A219" s="3">
         <v>9841</v>
       </c>
@@ -8170,7 +8169,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="220" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A220" s="3">
         <v>9840</v>
       </c>
@@ -8205,7 +8204,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="221" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A221" s="3">
         <v>9887</v>
       </c>
@@ -8240,7 +8239,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="222" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A222" s="3">
         <v>9883</v>
       </c>
@@ -8275,7 +8274,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="223" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A223" s="3">
         <v>9879</v>
       </c>
@@ -8310,7 +8309,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="224" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A224" s="3">
         <v>9911</v>
       </c>
@@ -8345,7 +8344,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="225" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A225" s="3">
         <v>9909</v>
       </c>
@@ -8380,7 +8379,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="226" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A226" s="3">
         <v>9907</v>
       </c>
@@ -8415,7 +8414,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="227" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A227" s="3">
         <v>9968</v>
       </c>
@@ -8450,7 +8449,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="228" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A228" s="3">
         <v>9988</v>
       </c>
@@ -8485,7 +8484,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="229" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A229" s="3">
         <v>9987</v>
       </c>
@@ -8520,7 +8519,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="230" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A230" s="3">
         <v>9985</v>
       </c>
@@ -8555,7 +8554,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="231" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A231" s="3">
         <v>10000</v>
       </c>
@@ -8590,7 +8589,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="232" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A232" s="3">
         <v>9999</v>
       </c>
@@ -8625,7 +8624,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="233" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A233" s="3">
         <v>9998</v>
       </c>
@@ -8660,7 +8659,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="234" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A234" s="3">
         <v>10004</v>
       </c>
@@ -8695,7 +8694,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="235" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A235" s="3">
         <v>10003</v>
       </c>
@@ -8730,7 +8729,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="236" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A236" s="3">
         <v>10018</v>
       </c>
@@ -8765,7 +8764,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="237" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A237" s="3">
         <v>10017</v>
       </c>
@@ -8800,7 +8799,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="238" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A238" s="3">
         <v>10013</v>
       </c>
@@ -8835,7 +8834,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="239" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A239" s="3">
         <v>10012</v>
       </c>
@@ -8870,7 +8869,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="240" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A240" s="3">
         <v>10033</v>
       </c>
@@ -8905,7 +8904,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="241" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A241" s="3">
         <v>10032</v>
       </c>
@@ -8940,7 +8939,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="242" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A242" s="3">
         <v>10031</v>
       </c>
@@ -8975,7 +8974,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="243" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A243" s="3">
         <v>10030</v>
       </c>
@@ -9010,7 +9009,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="244" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A244" s="3">
         <v>10049</v>
       </c>
@@ -9045,7 +9044,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="245" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A245" s="3">
         <v>10048</v>
       </c>
@@ -9080,7 +9079,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="246" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A246" s="3">
         <v>10158</v>
       </c>
@@ -9115,7 +9114,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="247" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A247" s="3">
         <v>10156</v>
       </c>
@@ -9150,7 +9149,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="248" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A248" s="3">
         <v>10164</v>
       </c>
@@ -9185,7 +9184,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="249" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A249" s="3">
         <v>10176</v>
       </c>
@@ -9220,7 +9219,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="250" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A250" s="3">
         <v>10174</v>
       </c>
@@ -9255,7 +9254,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="251" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A251" s="3">
         <v>10172</v>
       </c>
@@ -9290,7 +9289,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="252" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A252" s="3">
         <v>10200</v>
       </c>
@@ -9325,7 +9324,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="253" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A253" s="3">
         <v>10201</v>
       </c>
@@ -9360,7 +9359,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="254" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A254" s="3">
         <v>10231</v>
       </c>
@@ -9395,7 +9394,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="255" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A255" s="3">
         <v>10232</v>
       </c>
@@ -9430,7 +9429,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="256" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A256" s="3">
         <v>10233</v>
       </c>
@@ -9465,7 +9464,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="257" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A257" s="3">
         <v>10240</v>
       </c>
@@ -9500,7 +9499,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="258" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A258" s="3">
         <v>10243</v>
       </c>
@@ -9535,7 +9534,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="259" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A259" s="3">
         <v>10245</v>
       </c>
@@ -9570,7 +9569,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="260" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A260" s="3">
         <v>10254</v>
       </c>
@@ -9605,7 +9604,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="261" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A261" s="3">
         <v>10255</v>
       </c>
@@ -9640,7 +9639,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="262" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A262" s="3">
         <v>10268</v>
       </c>
@@ -9675,7 +9674,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="263" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A263" s="3">
         <v>10269</v>
       </c>
@@ -9710,7 +9709,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="264" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A264" s="3">
         <v>10271</v>
       </c>
@@ -9745,7 +9744,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="265" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A265" s="3">
         <v>10272</v>
       </c>
@@ -9780,7 +9779,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="266" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A266" s="3">
         <v>10273</v>
       </c>
@@ -9815,7 +9814,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="267" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A267" s="3">
         <v>10275</v>
       </c>
@@ -9850,7 +9849,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="268" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A268" s="3">
         <v>10276</v>
       </c>
@@ -9885,7 +9884,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="269" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A269" s="3">
         <v>10287</v>
       </c>
@@ -9920,7 +9919,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="270" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A270" s="3">
         <v>10288</v>
       </c>
@@ -9955,7 +9954,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="271" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A271" s="3">
         <v>10293</v>
       </c>
@@ -9990,7 +9989,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="272" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A272" s="3">
         <v>10297</v>
       </c>
@@ -10025,7 +10024,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="273" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A273" s="3">
         <v>10294</v>
       </c>
@@ -10060,7 +10059,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="274" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A274" s="3">
         <v>10304</v>
       </c>
@@ -10095,7 +10094,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="275" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A275" s="3">
         <v>10317</v>
       </c>
@@ -10130,7 +10129,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="276" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A276" s="3">
         <v>10318</v>
       </c>
@@ -10165,7 +10164,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="277" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A277" s="3">
         <v>10322</v>
       </c>
@@ -10200,7 +10199,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="278" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A278" s="3">
         <v>10327</v>
       </c>
@@ -10235,7 +10234,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="279" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A279" s="3">
         <v>10328</v>
       </c>
@@ -10270,7 +10269,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="280" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A280" s="3">
         <v>10333</v>
       </c>
@@ -10305,7 +10304,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="281" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A281" s="3">
         <v>10343</v>
       </c>
@@ -10340,7 +10339,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="282" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A282" s="3">
         <v>10345</v>
       </c>
@@ -10375,7 +10374,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="283" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A283" s="3">
         <v>10349</v>
       </c>
@@ -10410,7 +10409,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="284" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A284" s="3">
         <v>10351</v>
       </c>
@@ -10445,7 +10444,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="285" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A285" s="3">
         <v>10352</v>
       </c>
@@ -10480,7 +10479,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="286" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A286" s="3">
         <v>10355</v>
       </c>
@@ -10515,7 +10514,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="287" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A287" s="3">
         <v>10356</v>
       </c>
@@ -10550,7 +10549,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="288" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A288" s="3">
         <v>10358</v>
       </c>
@@ -10585,7 +10584,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="289" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A289" s="3">
         <v>10359</v>
       </c>
@@ -10620,7 +10619,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="290" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A290" s="3">
         <v>10360</v>
       </c>
@@ -10655,7 +10654,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="291" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A291" s="3">
         <v>10362</v>
       </c>
@@ -10690,7 +10689,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="292" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A292" s="3">
         <v>10363</v>
       </c>
@@ -10725,7 +10724,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="293" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A293" s="3">
         <v>10364</v>
       </c>
@@ -10760,7 +10759,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="294" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A294" s="3">
         <v>10367</v>
       </c>
@@ -10795,7 +10794,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="295" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A295" s="3">
         <v>10370</v>
       </c>
@@ -10830,7 +10829,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="296" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A296" s="3">
         <v>10371</v>
       </c>
@@ -10865,7 +10864,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="297" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A297" s="3">
         <v>10372</v>
       </c>
@@ -10900,7 +10899,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="298" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A298" s="3">
         <v>10373</v>
       </c>
@@ -10935,7 +10934,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="299" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A299" s="3">
         <v>10374</v>
       </c>
@@ -10970,7 +10969,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="300" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A300" s="3">
         <v>10375</v>
       </c>
@@ -11005,7 +11004,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="301" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A301" s="3">
         <v>10376</v>
       </c>
@@ -11040,7 +11039,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="302" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A302" s="3">
         <v>10377</v>
       </c>
@@ -11075,7 +11074,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="303" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A303" s="3">
         <v>10381</v>
       </c>
@@ -11110,7 +11109,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="304" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A304" s="3">
         <v>10388</v>
       </c>
@@ -11145,7 +11144,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="305" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A305" s="3">
         <v>10390</v>
       </c>
@@ -11180,7 +11179,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="306" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A306" s="3">
         <v>10391</v>
       </c>
@@ -11215,7 +11214,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="307" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A307" s="3">
         <v>10392</v>
       </c>
@@ -11250,7 +11249,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="308" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A308" s="3">
         <v>10394</v>
       </c>
@@ -11285,7 +11284,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="309" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A309" s="3">
         <v>10406</v>
       </c>
@@ -11320,7 +11319,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="310" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A310" s="3">
         <v>10408</v>
       </c>
@@ -11355,7 +11354,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="311" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A311" s="3">
         <v>10411</v>
       </c>
@@ -11390,7 +11389,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="312" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A312" s="3">
         <v>10413</v>
       </c>
@@ -11425,7 +11424,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="313" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A313" s="3">
         <v>10418</v>
       </c>
@@ -11460,7 +11459,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="314" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A314" s="3">
         <v>10426</v>
       </c>
@@ -11495,7 +11494,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="315" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A315" s="3">
         <v>10427</v>
       </c>
@@ -11530,7 +11529,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="316" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A316" s="3">
         <v>10428</v>
       </c>
@@ -11565,7 +11564,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="317" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A317" s="3">
         <v>10430</v>
       </c>
@@ -11600,7 +11599,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="318" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A318" s="3">
         <v>10431</v>
       </c>
@@ -11635,7 +11634,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="319" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A319" s="3">
         <v>10440</v>
       </c>
@@ -11670,7 +11669,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="320" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A320" s="3">
         <v>10441</v>
       </c>
@@ -11705,7 +11704,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="321" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A321" s="3">
         <v>10442</v>
       </c>
@@ -11740,7 +11739,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="322" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A322" s="3">
         <v>10443</v>
       </c>
@@ -11775,7 +11774,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="323" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A323" s="3">
         <v>10449</v>
       </c>
@@ -11810,7 +11809,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="324" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A324" s="3">
         <v>10454</v>
       </c>
@@ -11845,7 +11844,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="325" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A325" s="3">
         <v>10455</v>
       </c>
@@ -11880,7 +11879,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="326" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A326" s="3">
         <v>10456</v>
       </c>
@@ -11915,7 +11914,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="327" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A327" s="3">
         <v>10457</v>
       </c>
@@ -11950,7 +11949,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="328" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A328" s="3">
         <v>10458</v>
       </c>
@@ -11985,7 +11984,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="329" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A329" s="3">
         <v>10460</v>
       </c>
@@ -12020,7 +12019,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="330" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A330" s="3">
         <v>10461</v>
       </c>
@@ -12055,7 +12054,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="331" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A331" s="3">
         <v>10462</v>
       </c>
@@ -12090,7 +12089,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="332" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A332" s="3">
         <v>10463</v>
       </c>
@@ -12125,7 +12124,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="333" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A333" s="3">
         <v>10468</v>
       </c>
@@ -12160,7 +12159,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="334" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A334" s="3">
         <v>10469</v>
       </c>
@@ -12195,7 +12194,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="335" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A335" s="3">
         <v>10471</v>
       </c>
@@ -12230,7 +12229,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="336" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A336" s="3">
         <v>10472</v>
       </c>
@@ -12265,7 +12264,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="337" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A337" s="3">
         <v>10473</v>
       </c>
@@ -12300,7 +12299,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="338" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A338" s="3">
         <v>10474</v>
       </c>
@@ -12335,7 +12334,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="339" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A339" s="3">
         <v>10475</v>
       </c>
@@ -12370,7 +12369,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="340" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A340" s="3">
         <v>10476</v>
       </c>
@@ -12405,7 +12404,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="341" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A341" s="3">
         <v>10477</v>
       </c>
@@ -12440,7 +12439,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="342" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A342" s="3">
         <v>10478</v>
       </c>
@@ -12475,7 +12474,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="343" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A343" s="3">
         <v>10483</v>
       </c>
@@ -12510,7 +12509,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="344" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A344" s="3">
         <v>10491</v>
       </c>
@@ -12545,7 +12544,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="345" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A345" s="3">
         <v>10490</v>
       </c>
@@ -12580,7 +12579,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="346" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A346" s="3">
         <v>10489</v>
       </c>
@@ -12615,7 +12614,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="347" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A347" s="3">
         <v>10503</v>
       </c>
@@ -12650,7 +12649,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="348" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A348" s="3">
         <v>10502</v>
       </c>
@@ -12685,7 +12684,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="349" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A349" s="3">
         <v>10495</v>
       </c>
@@ -12720,7 +12719,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="350" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A350" s="3">
         <v>10521</v>
       </c>
@@ -12755,7 +12754,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="351" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A351" s="3">
         <v>10520</v>
       </c>
@@ -12790,7 +12789,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="352" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A352" s="3">
         <v>10519</v>
       </c>
@@ -12825,7 +12824,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="353" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A353" s="3">
         <v>10518</v>
       </c>
@@ -12860,7 +12859,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="354" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A354" s="3">
         <v>10517</v>
       </c>
@@ -12895,7 +12894,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="355" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A355" s="3">
         <v>10516</v>
       </c>
@@ -12930,7 +12929,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="356" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A356" s="3">
         <v>10515</v>
       </c>
@@ -12965,7 +12964,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="357" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A357" s="3">
         <v>10509</v>
       </c>
@@ -13000,7 +12999,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="358" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A358" s="3">
         <v>10507</v>
       </c>
@@ -13035,7 +13034,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="359" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A359" s="3">
         <v>10541</v>
       </c>
@@ -13070,7 +13069,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="360" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A360" s="3">
         <v>10536</v>
       </c>
@@ -13105,7 +13104,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="361" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A361" s="3">
         <v>10535</v>
       </c>
@@ -13140,7 +13139,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="362" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A362" s="3">
         <v>10534</v>
       </c>
@@ -13175,7 +13174,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="363" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A363" s="3">
         <v>10533</v>
       </c>
@@ -13210,7 +13209,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="364" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A364" s="3">
         <v>10532</v>
       </c>
@@ -13245,7 +13244,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="365" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A365" s="3">
         <v>10531</v>
       </c>
@@ -13280,7 +13279,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="366" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A366" s="3">
         <v>10530</v>
       </c>
@@ -13315,7 +13314,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="367" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A367" s="3">
         <v>10523</v>
       </c>
@@ -13350,7 +13349,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="368" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A368" s="3">
         <v>10550</v>
       </c>
@@ -13385,7 +13384,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="369" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A369" s="3">
         <v>10549</v>
       </c>
@@ -13420,7 +13419,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="370" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A370" s="3">
         <v>10548</v>
       </c>
@@ -13455,7 +13454,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="371" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A371" s="3">
         <v>10547</v>
       </c>
@@ -13490,7 +13489,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="372" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A372" s="3">
         <v>10551</v>
       </c>
@@ -13525,7 +13524,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="373" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A373" s="3">
         <v>10565</v>
       </c>
@@ -13560,7 +13559,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="374" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A374" s="3">
         <v>10564</v>
       </c>
@@ -13595,7 +13594,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="375" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A375" s="3">
         <v>10576</v>
       </c>
@@ -13630,7 +13629,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="376" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A376" s="3">
         <v>10575</v>
       </c>
@@ -13665,7 +13664,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="377" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A377" s="3">
         <v>10599</v>
       </c>
@@ -13700,7 +13699,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="378" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A378" s="3">
         <v>10598</v>
       </c>
@@ -13735,7 +13734,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="379" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A379" s="3">
         <v>10597</v>
       </c>
@@ -13770,7 +13769,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="380" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A380" s="3">
         <v>10591</v>
       </c>
@@ -13805,7 +13804,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="381" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A381" s="3">
         <v>10581</v>
       </c>
@@ -13840,7 +13839,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="382" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A382" s="3">
         <v>10580</v>
       </c>
@@ -13875,7 +13874,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="383" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A383" s="3">
         <v>10579</v>
       </c>
@@ -13910,7 +13909,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="384" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A384" s="3">
         <v>10578</v>
       </c>
@@ -13945,7 +13944,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="385" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A385" s="3">
         <v>10613</v>
       </c>
@@ -13980,7 +13979,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="386" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A386" s="3">
         <v>10610</v>
       </c>
@@ -14015,7 +14014,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="387" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A387" s="3">
         <v>10600</v>
       </c>
@@ -14050,7 +14049,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="388" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A388" s="3">
         <v>10621</v>
       </c>
@@ -14085,7 +14084,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="389" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A389" s="3">
         <v>10616</v>
       </c>
@@ -14120,7 +14119,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="390" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A390" s="3">
         <v>10614</v>
       </c>
@@ -14155,7 +14154,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="391" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A391" s="3">
         <v>10633</v>
       </c>
@@ -14190,7 +14189,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="392" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A392" s="3">
         <v>10627</v>
       </c>
@@ -14225,7 +14224,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="393" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A393" s="3">
         <v>10626</v>
       </c>
@@ -14260,7 +14259,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="394" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A394" s="3">
         <v>10649</v>
       </c>
@@ -14295,7 +14294,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="395" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A395" s="3">
         <v>10648</v>
       </c>
@@ -14330,7 +14329,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="396" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A396" s="3">
         <v>10647</v>
       </c>
@@ -14365,7 +14364,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="397" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A397" s="3">
         <v>10646</v>
       </c>
@@ -14400,7 +14399,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="398" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A398" s="3">
         <v>10646</v>
       </c>
@@ -14435,7 +14434,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="399" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A399" s="3">
         <v>10645</v>
       </c>
@@ -14470,7 +14469,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="400" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A400" s="3">
         <v>10644</v>
       </c>
@@ -14505,7 +14504,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="401" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A401" s="3">
         <v>10673</v>
       </c>
@@ -14540,7 +14539,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="402" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A402" s="3">
         <v>10672</v>
       </c>
@@ -14575,7 +14574,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="403" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A403" s="3">
         <v>10671</v>
       </c>
@@ -14610,7 +14609,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="404" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A404" s="3">
         <v>10670</v>
       </c>
@@ -14645,7 +14644,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="405" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A405" s="3">
         <v>10669</v>
       </c>
@@ -14680,7 +14679,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="406" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A406" s="3">
         <v>10662</v>
       </c>
@@ -14715,7 +14714,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="407" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A407" s="3">
         <v>10661</v>
       </c>
@@ -14750,7 +14749,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="408" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A408" s="3">
         <v>10659</v>
       </c>
@@ -14785,7 +14784,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="409" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A409" s="3">
         <v>10658</v>
       </c>
@@ -14820,7 +14819,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="410" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A410" s="3">
         <v>10656</v>
       </c>
@@ -14855,7 +14854,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="411" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A411" s="3">
         <v>10655</v>
       </c>
@@ -14890,7 +14889,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="412" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A412" s="3">
         <v>10701</v>
       </c>
@@ -14925,7 +14924,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="413" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A413" s="3">
         <v>10700</v>
       </c>
@@ -14960,7 +14959,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="414" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A414" s="3">
         <v>10696</v>
       </c>
@@ -14995,7 +14994,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="415" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A415" s="3">
         <v>10695</v>
       </c>
@@ -15030,7 +15029,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="416" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A416" s="3">
         <v>10694</v>
       </c>
@@ -15065,7 +15064,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="417" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A417" s="3">
         <v>10693</v>
       </c>
@@ -15100,7 +15099,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="418" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A418" s="3">
         <v>10692</v>
       </c>
@@ -15135,7 +15134,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="419" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A419" s="3">
         <v>10691</v>
       </c>
@@ -15170,7 +15169,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="420" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A420" s="3">
         <v>10690</v>
       </c>
@@ -15205,7 +15204,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="421" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A421" s="3">
         <v>10689</v>
       </c>
@@ -15240,7 +15239,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="422" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A422" s="3">
         <v>10688</v>
       </c>
@@ -15275,7 +15274,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="423" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A423" s="3">
         <v>10687</v>
       </c>
@@ -15310,7 +15309,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="424" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A424" s="3">
         <v>10686</v>
       </c>
@@ -15345,7 +15344,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="425" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A425" s="3">
         <v>10685</v>
       </c>
@@ -15380,7 +15379,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="426" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A426" s="3">
         <v>10684</v>
       </c>
@@ -15415,7 +15414,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="427" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A427" s="3">
         <v>10683</v>
       </c>
@@ -15450,7 +15449,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="428" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A428" s="3">
         <v>10682</v>
       </c>
@@ -15485,7 +15484,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="429" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A429" s="3">
         <v>10716</v>
       </c>
@@ -15520,7 +15519,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="430" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A430" s="3">
         <v>10715</v>
       </c>
@@ -15555,7 +15554,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="431" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A431" s="3">
         <v>10711</v>
       </c>
@@ -15590,7 +15589,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="432" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A432" s="3">
         <v>10704</v>
       </c>
@@ -15625,7 +15624,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="433" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A433" s="3">
         <v>10726</v>
       </c>
@@ -15660,7 +15659,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="434" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A434" s="3">
         <v>10725</v>
       </c>
@@ -15695,7 +15694,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="435" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A435" s="3">
         <v>10724</v>
       </c>
@@ -15730,7 +15729,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="436" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A436" s="3">
         <v>10720</v>
       </c>
@@ -15765,7 +15764,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="437" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A437" s="3">
         <v>10719</v>
       </c>
@@ -15800,7 +15799,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="438" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A438" s="3">
         <v>10752</v>
       </c>
@@ -15835,7 +15834,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="439" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A439" s="3">
         <v>10749</v>
       </c>
@@ -15870,7 +15869,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="440" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A440" s="3">
         <v>10748</v>
       </c>
@@ -15905,7 +15904,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="441" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A441" s="3">
         <v>10747</v>
       </c>
@@ -15940,7 +15939,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="442" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A442" s="3">
         <v>10745</v>
       </c>
@@ -15975,7 +15974,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="443" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A443" s="3">
         <v>10744</v>
       </c>
@@ -16010,7 +16009,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="444" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A444" s="3">
         <v>10743</v>
       </c>
@@ -16045,7 +16044,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="445" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A445" s="3">
         <v>10741</v>
       </c>
@@ -16080,7 +16079,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="446" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A446" s="3">
         <v>10739</v>
       </c>
@@ -16115,7 +16114,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="447" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A447" s="3">
         <v>10736</v>
       </c>
@@ -16150,7 +16149,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="448" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A448" s="3">
         <v>10735</v>
       </c>
@@ -16185,7 +16184,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="449" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A449" s="3">
         <v>10734</v>
       </c>
@@ -16220,7 +16219,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="450" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A450" s="3">
         <v>10733</v>
       </c>
@@ -16255,7 +16254,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="451" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A451" s="3">
         <v>10732</v>
       </c>
@@ -16290,7 +16289,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="452" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A452" s="3">
         <v>10732</v>
       </c>
@@ -16325,7 +16324,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="453" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A453" s="3">
         <v>10781</v>
       </c>
@@ -16360,7 +16359,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="454" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A454" s="3">
         <v>10780</v>
       </c>
@@ -16395,7 +16394,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="455" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A455" s="3">
         <v>10779</v>
       </c>
@@ -16430,7 +16429,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="456" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A456" s="3">
         <v>10778</v>
       </c>
@@ -16465,7 +16464,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="457" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A457" s="3">
         <v>10777</v>
       </c>
@@ -16500,7 +16499,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="458" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A458" s="3">
         <v>10776</v>
       </c>
@@ -16535,7 +16534,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="459" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A459" s="3">
         <v>10775</v>
       </c>
@@ -16570,7 +16569,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="460" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A460" s="3">
         <v>10774</v>
       </c>
@@ -16605,7 +16604,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="461" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A461" s="3">
         <v>10773</v>
       </c>
@@ -16640,7 +16639,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="462" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A462" s="3">
         <v>10772</v>
       </c>
@@ -16675,7 +16674,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="463" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A463" s="3">
         <v>10771</v>
       </c>
@@ -16710,7 +16709,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="464" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A464" s="3">
         <v>10768</v>
       </c>
@@ -16745,7 +16744,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="465" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A465" s="3">
         <v>10767</v>
       </c>
@@ -16780,7 +16779,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="466" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A466" s="3">
         <v>10766</v>
       </c>
@@ -16815,7 +16814,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="467" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A467" s="3">
         <v>10765</v>
       </c>
@@ -16850,7 +16849,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="468" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A468" s="3">
         <v>10764</v>
       </c>
@@ -16885,7 +16884,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="469" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A469" s="3">
         <v>10763</v>
       </c>
@@ -16920,7 +16919,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="470" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A470" s="3">
         <v>10762</v>
       </c>
@@ -16955,7 +16954,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="471" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A471" s="3">
         <v>10761</v>
       </c>
@@ -16990,7 +16989,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="472" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A472" s="3">
         <v>10760</v>
       </c>
@@ -17025,7 +17024,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="473" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A473" s="3">
         <v>10759</v>
       </c>
@@ -17060,7 +17059,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="474" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A474" s="3">
         <v>10758</v>
       </c>
@@ -17095,7 +17094,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="475" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A475" s="3">
         <v>10756</v>
       </c>
@@ -17130,7 +17129,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="476" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A476" s="3">
         <v>10791</v>
       </c>
@@ -17165,7 +17164,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="477" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A477" s="3">
         <v>10788</v>
       </c>
@@ -17200,7 +17199,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="478" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A478" s="3">
         <v>10799</v>
       </c>
@@ -17235,7 +17234,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="479" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A479" s="3">
         <v>10800</v>
       </c>
@@ -17270,7 +17269,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="480" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A480" s="3">
         <v>10817</v>
       </c>
@@ -17305,7 +17304,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="481" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A481" s="3">
         <v>10819</v>
       </c>
@@ -17340,7 +17339,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="482" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A482" s="3">
         <v>10820</v>
       </c>
@@ -17375,7 +17374,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="483" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A483" s="3">
         <v>10821</v>
       </c>
@@ -17410,7 +17409,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="484" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A484" s="3">
         <v>10822</v>
       </c>
@@ -17445,7 +17444,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="485" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A485" s="3">
         <v>10823</v>
       </c>
@@ -17480,7 +17479,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="486" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A486" s="3">
         <v>10825</v>
       </c>
@@ -17515,7 +17514,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="487" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A487" s="3">
         <v>10826</v>
       </c>
@@ -17550,7 +17549,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="488" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A488" s="3">
         <v>10827</v>
       </c>
@@ -17585,7 +17584,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="489" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A489" s="3">
         <v>10828</v>
       </c>
@@ -17620,7 +17619,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="490" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A490" s="3">
         <v>10831</v>
       </c>
@@ -17655,7 +17654,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="491" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A491" s="3">
         <v>10832</v>
       </c>
@@ -17690,7 +17689,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="492" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A492" s="3">
         <v>10833</v>
       </c>
@@ -17725,7 +17724,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="493" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A493" s="3">
         <v>10838</v>
       </c>
@@ -17760,7 +17759,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="494" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A494" s="3">
         <v>10839</v>
       </c>
@@ -17795,7 +17794,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="495" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A495" s="3">
         <v>10840</v>
       </c>
@@ -17830,7 +17829,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="496" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A496" s="3">
         <v>10843</v>
       </c>
@@ -17865,7 +17864,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="497" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A497" s="3">
         <v>10845</v>
       </c>
@@ -17900,7 +17899,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="498" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A498" s="3">
         <v>10846</v>
       </c>
@@ -17935,7 +17934,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="499" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A499" s="3">
         <v>10848</v>
       </c>
@@ -17970,7 +17969,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="500" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A500" s="3">
         <v>10849</v>
       </c>
@@ -18005,7 +18004,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="501" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A501" s="3">
         <v>10850</v>
       </c>
@@ -18040,7 +18039,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="502" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A502" s="3">
         <v>10851</v>
       </c>
@@ -18075,7 +18074,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="503" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A503" s="3">
         <v>10852</v>
       </c>
@@ -18110,7 +18109,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="504" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A504" s="3">
         <v>10860</v>
       </c>
@@ -18145,7 +18144,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="505" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A505" s="3">
         <v>10861</v>
       </c>
@@ -18180,7 +18179,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="506" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A506" s="3">
         <v>10862</v>
       </c>
@@ -18215,7 +18214,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="507" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A507" s="3">
         <v>10864</v>
       </c>
@@ -18250,7 +18249,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="508" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A508" s="3">
         <v>10866</v>
       </c>
@@ -18285,7 +18284,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="509" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A509" s="3">
         <v>10869</v>
       </c>
@@ -18320,7 +18319,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="510" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A510" s="3">
         <v>10870</v>
       </c>
@@ -18355,7 +18354,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="511" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A511" s="3">
         <v>10871</v>
       </c>
@@ -18390,7 +18389,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="512" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A512" s="3">
         <v>10872</v>
       </c>
@@ -18425,7 +18424,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="513" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A513" s="3">
         <v>10873</v>
       </c>
@@ -18460,7 +18459,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="514" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A514" s="3">
         <v>10874</v>
       </c>
@@ -18495,7 +18494,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="515" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A515" s="3">
         <v>10881</v>
       </c>
@@ -18530,7 +18529,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="516" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A516" s="3">
         <v>10882</v>
       </c>
@@ -18565,7 +18564,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="517" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A517" s="3">
         <v>10883</v>
       </c>
@@ -18600,7 +18599,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="518" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A518" s="3">
         <v>10887</v>
       </c>
@@ -18635,7 +18634,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="519" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A519" s="3">
         <v>10888</v>
       </c>
@@ -18670,7 +18669,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="520" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A520" s="3">
         <v>10889</v>
       </c>
@@ -18705,7 +18704,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="521" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A521" s="3">
         <v>10894</v>
       </c>
@@ -18740,7 +18739,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="522" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A522" s="3">
         <v>10899</v>
       </c>
@@ -18775,7 +18774,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="523" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A523" s="3">
         <v>10900</v>
       </c>
@@ -18810,7 +18809,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="524" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A524" s="3">
         <v>10901</v>
       </c>
@@ -18845,7 +18844,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="525" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A525" s="3">
         <v>10902</v>
       </c>
@@ -18880,7 +18879,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="526" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A526" s="3">
         <v>10903</v>
       </c>
@@ -18915,7 +18914,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="527" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A527" s="3">
         <v>10904</v>
       </c>
@@ -18950,7 +18949,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="528" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A528" s="3">
         <v>10905</v>
       </c>
@@ -18985,7 +18984,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="529" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A529" s="3">
         <v>10906</v>
       </c>
@@ -19020,7 +19019,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="530" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A530" s="3">
         <v>10907</v>
       </c>
@@ -19055,7 +19054,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="531" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A531" s="3">
         <v>10908</v>
       </c>
@@ -19090,7 +19089,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="532" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A532" s="3">
         <v>10910</v>
       </c>
@@ -19125,7 +19124,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="533" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A533" s="3">
         <v>10913</v>
       </c>
@@ -19160,7 +19159,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="534" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A534" s="3">
         <v>10914</v>
       </c>
@@ -19195,7 +19194,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="535" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A535" s="3">
         <v>10915</v>
       </c>
@@ -19230,7 +19229,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="536" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A536" s="3">
         <v>10918</v>
       </c>
@@ -19265,7 +19264,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="537" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A537" s="3">
         <v>10919</v>
       </c>
@@ -19300,7 +19299,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="538" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A538" s="3">
         <v>10920</v>
       </c>
@@ -19335,7 +19334,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="539" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A539" s="3">
         <v>10927</v>
       </c>
@@ -19370,7 +19369,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="540" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A540" s="3">
         <v>10928</v>
       </c>
@@ -19405,7 +19404,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="541" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A541" s="3">
         <v>10931</v>
       </c>
@@ -19440,7 +19439,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="542" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A542" s="3">
         <v>10932</v>
       </c>
@@ -19475,7 +19474,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="543" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A543" s="3">
         <v>10933</v>
       </c>
@@ -19510,7 +19509,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="544" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A544" s="3">
         <v>10935</v>
       </c>
@@ -19545,7 +19544,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="545" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A545" s="3">
         <v>10939</v>
       </c>
@@ -19580,7 +19579,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="546" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A546" s="3">
         <v>10941</v>
       </c>
@@ -19615,7 +19614,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="547" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A547" s="3">
         <v>10942</v>
       </c>
@@ -19650,7 +19649,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="548" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A548" s="3">
         <v>10943</v>
       </c>
@@ -19685,7 +19684,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="549" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A549" s="3">
         <v>10944</v>
       </c>
@@ -19720,7 +19719,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="550" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A550" s="3">
         <v>10945</v>
       </c>
@@ -19755,7 +19754,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="551" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A551" s="3">
         <v>10946</v>
       </c>
@@ -19790,7 +19789,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="552" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A552" s="3">
         <v>10947</v>
       </c>
@@ -19825,7 +19824,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="553" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A553" s="3">
         <v>10948</v>
       </c>
@@ -19860,7 +19859,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="554" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A554" s="3">
         <v>10949</v>
       </c>
@@ -19895,7 +19894,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="555" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A555" s="3">
         <v>10950</v>
       </c>
@@ -19930,7 +19929,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="556" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A556" s="3">
         <v>10951</v>
       </c>
@@ -19965,7 +19964,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="557" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A557" s="3">
         <v>10954</v>
       </c>
@@ -20000,7 +19999,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="558" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A558" s="3">
         <v>10960</v>
       </c>
@@ -20035,7 +20034,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="559" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A559" s="3">
         <v>10964</v>
       </c>
@@ -20070,7 +20069,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="560" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A560" s="3">
         <v>10965</v>
       </c>
@@ -20105,7 +20104,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="561" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A561" s="3">
         <v>10966</v>
       </c>
@@ -20140,7 +20139,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="562" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A562" s="3">
         <v>10967</v>
       </c>
@@ -20175,7 +20174,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="563" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A563" s="3">
         <v>10969</v>
       </c>
@@ -20210,7 +20209,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="564" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A564" s="3">
         <v>10970</v>
       </c>
@@ -20245,7 +20244,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="565" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A565" s="3">
         <v>10972</v>
       </c>
@@ -20280,7 +20279,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="566" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A566" s="3">
         <v>10982</v>
       </c>
@@ -20315,7 +20314,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="567" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A567" s="3">
         <v>10983</v>
       </c>
@@ -20350,7 +20349,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="568" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A568" s="3">
         <v>10984</v>
       </c>
@@ -20385,7 +20384,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="569" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A569" s="3">
         <v>10985</v>
       </c>
@@ -20420,7 +20419,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="570" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A570" s="3">
         <v>10986</v>
       </c>
@@ -20455,7 +20454,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="571" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A571" s="3">
         <v>10987</v>
       </c>
@@ -20490,7 +20489,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="572" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A572" s="3">
         <v>10988</v>
       </c>
@@ -20525,7 +20524,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="573" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A573" s="3">
         <v>10989</v>
       </c>
@@ -20560,7 +20559,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="574" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A574" s="3">
         <v>10967</v>
       </c>
@@ -20595,7 +20594,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="575" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A575" s="3">
         <v>10996</v>
       </c>
@@ -20630,7 +20629,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="576" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A576" s="3">
         <v>10998</v>
       </c>
@@ -20665,7 +20664,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="577" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A577" s="3">
         <v>11000</v>
       </c>
@@ -20700,7 +20699,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="578" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A578" s="3">
         <v>11001</v>
       </c>
@@ -20735,7 +20734,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="579" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A579" s="3">
         <v>11002</v>
       </c>
@@ -20770,7 +20769,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="580" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A580" s="3">
         <v>11003</v>
       </c>
@@ -20805,7 +20804,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="581" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A581" s="3">
         <v>11006</v>
       </c>
@@ -20840,7 +20839,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="582" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A582" s="3">
         <v>11007</v>
       </c>
@@ -20875,7 +20874,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="583" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A583" s="3">
         <v>11008</v>
       </c>
@@ -20910,7 +20909,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="584" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A584" s="3">
         <v>11009</v>
       </c>
@@ -20945,7 +20944,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="585" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A585" s="3">
         <v>11013</v>
       </c>
@@ -20980,7 +20979,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="586" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A586" s="3">
         <v>11014</v>
       </c>
@@ -21015,7 +21014,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="587" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A587" s="3">
         <v>11015</v>
       </c>
@@ -21050,7 +21049,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="588" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A588" s="3">
         <v>11017</v>
       </c>
@@ -21085,7 +21084,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="589" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A589" s="3">
         <v>11018</v>
       </c>
@@ -21120,7 +21119,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="590" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A590" s="3">
         <v>11023</v>
       </c>
@@ -21155,7 +21154,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="591" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A591" s="3">
         <v>11024</v>
       </c>
@@ -21190,7 +21189,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="592" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A592" s="3">
         <v>11027</v>
       </c>
@@ -21225,7 +21224,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="593" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A593" s="3">
         <v>11028</v>
       </c>
@@ -21260,7 +21259,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="594" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A594" s="3">
         <v>11036</v>
       </c>
@@ -21295,7 +21294,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="595" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A595" s="3">
         <v>11037</v>
       </c>
@@ -21330,7 +21329,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="596" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A596" s="3">
         <v>11041</v>
       </c>
@@ -21365,7 +21364,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="597" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A597" s="3">
         <v>11043</v>
       </c>
@@ -21400,7 +21399,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="598" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A598" s="3">
         <v>11044</v>
       </c>
@@ -21435,7 +21434,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="599" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A599" s="3">
         <v>11045</v>
       </c>
@@ -21470,7 +21469,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="600" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A600" s="3">
         <v>11046</v>
       </c>
@@ -21505,7 +21504,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="601" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A601" s="3">
         <v>11047</v>
       </c>
@@ -21540,7 +21539,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="602" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A602" s="3">
         <v>11053</v>
       </c>
@@ -21575,7 +21574,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="603" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A603" s="3">
         <v>11056</v>
       </c>
@@ -21610,7 +21609,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="604" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A604" s="3">
         <v>11057</v>
       </c>
@@ -21645,7 +21644,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="605" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A605" s="3">
         <v>11058</v>
       </c>
@@ -21680,7 +21679,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="606" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A606" s="3">
         <v>11059</v>
       </c>
@@ -21715,7 +21714,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="607" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A607" s="3">
         <v>11060</v>
       </c>
@@ -21750,7 +21749,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="608" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A608" s="3">
         <v>11061</v>
       </c>
@@ -21785,7 +21784,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="609" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A609" s="3">
         <v>11062</v>
       </c>
@@ -21820,7 +21819,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="610" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A610" s="3">
         <v>11063</v>
       </c>
@@ -21855,7 +21854,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="611" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A611" s="3">
         <v>11064</v>
       </c>
@@ -21890,7 +21889,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="612" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A612" s="3">
         <v>11065</v>
       </c>
@@ -21925,7 +21924,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="613" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A613" s="3">
         <v>11072</v>
       </c>
@@ -21960,7 +21959,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="614" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A614" s="3">
         <v>11073</v>
       </c>
@@ -21995,7 +21994,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="615" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A615" s="3">
         <v>11076</v>
       </c>
@@ -22030,7 +22029,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="616" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A616" s="3">
         <v>11077</v>
       </c>
@@ -22065,7 +22064,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="617" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A617" s="3">
         <v>11078</v>
       </c>
@@ -22100,7 +22099,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="618" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A618" s="3">
         <v>11081</v>
       </c>
@@ -22135,7 +22134,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="619" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A619" s="3">
         <v>11083</v>
       </c>
@@ -22170,7 +22169,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="620" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A620" s="3">
         <v>11084</v>
       </c>
@@ -22205,7 +22204,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="621" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A621" s="3">
         <v>11085</v>
       </c>
@@ -22240,7 +22239,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="622" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A622" s="3">
         <v>11095</v>
       </c>
@@ -22275,7 +22274,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="623" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A623" s="3">
         <v>11100</v>
       </c>
@@ -22310,7 +22309,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="624" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A624" s="3">
         <v>11099</v>
       </c>
@@ -22345,7 +22344,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="625" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A625" s="3">
         <v>11093</v>
       </c>
@@ -30081,11 +30080,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A3:K753" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="6">
-      <filters blank="1">
-        <dateGroupItem year="2026" month="7" dateTimeGrouping="month"/>
-      </filters>
-    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:K753">
       <sortCondition ref="I3:I753"/>
     </sortState>
